--- a/output/forms/滨海湾施工输入清单.xlsx
+++ b/output/forms/滨海湾施工输入清单.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="R6cf117a8f4454e55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计决策" sheetId="2" r:id="Red18933b25294340"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="家电清单" sheetId="3" r:id="R5b8d9e6e7ef64490"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="R40e2ddf5d920432f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计决策" sheetId="2" r:id="R0a1a5f63e7284778"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="家电清单" sheetId="3" r:id="Rfc8eb7af8b0a4863"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -318,7 +318,7 @@
         <x:color rgb="FF274E13"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
@@ -329,7 +329,7 @@
         <x:color rgb="FF274E13"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
@@ -339,7 +339,7 @@
         <x:color rgb="FF783F04"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE5CD"/>
         </x:patternFill>
       </x:fill>
@@ -350,7 +350,7 @@
         <x:color rgb="FF274E13"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
@@ -360,7 +360,7 @@
         <x:color rgb="FF7F6000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -818,7 +818,7 @@
       </x:c>
       <x:c r="B16" s="39" t="n">
         <x:f>COUNTIF('家电清单'!Q2:Q19,"已确认")</x:f>
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C16" s="26"/>
       <x:c r="D16" s="26"/>
@@ -918,11 +918,15 @@
       <x:c r="G2" s="49" t="str">
         <x:v>Master A</x:v>
       </x:c>
-      <x:c r="H2" s="47" t="str"/>
+      <x:c r="H2" s="47"/>
       <x:c r="I2" s="49" t="str">
         <x:v>需证据</x:v>
       </x:c>
-      <x:c r="J2" s="49" t="str"/>
+      <x:c r="J2" s="49" t="str">
+        <x:v>https://s3.poliform.it/2025/04/Poliform_Architectural_2024.pdf
+freestanding wardrobe and wall mounted Pivot
+</x:v>
+      </x:c>
       <x:c r="K2" s="47" t="str">
         <x:v>用户已确认 Master A 更符合实际开门贴墙关系；当前 IFC 无宿主洞口且 OperationType=NOTDEFINED</x:v>
       </x:c>
@@ -952,12 +956,14 @@
       <x:c r="F3" s="48" t="str">
         <x:v>Entry A（靠进入后顺手侧且避开门扇/门套）</x:v>
       </x:c>
-      <x:c r="G3" s="49" t="str"/>
-      <x:c r="H3" s="47" t="str"/>
+      <x:c r="G3" s="49" t="str">
+        <x:v>Entry A</x:v>
+      </x:c>
+      <x:c r="H3" s="47"/>
       <x:c r="I3" s="49" t="str">
         <x:v>待填写</x:v>
       </x:c>
-      <x:c r="J3" s="49" t="str"/>
+      <x:c r="J3" s="49"/>
       <x:c r="K3" s="47" t="str">
         <x:v>门口控制应位于真实墙面并满足门扇和柜门操作</x:v>
       </x:c>
@@ -987,12 +993,16 @@
       <x:c r="F4" s="48" t="str">
         <x:v>客厅双控；书房双控；餐厅双控；照明总控，优先一体四位或相邻同高分组</x:v>
       </x:c>
-      <x:c r="G4" s="49" t="str"/>
-      <x:c r="H4" s="47" t="str"/>
+      <x:c r="G4" s="49" t="str">
+        <x:v>这款怎么样？matter 协议？那是什么？knx吗？可以安卓用吗？苹果手机是可以用倒是</x:v>
+      </x:c>
+      <x:c r="H4" s="47"/>
       <x:c r="I4" s="49" t="str">
         <x:v>待填写</x:v>
       </x:c>
-      <x:c r="J4" s="49" t="str"/>
+      <x:c r="J4" s="49" t="str">
+        <x:v>【淘宝】假一赔四 https://e.tb.cn/h.87aSpFYZgStgIgK?tk=DBrSTaSu8bF CZ057 「JINK Switch EGG智能墙壁开关场景EGG直连全屋智能家居Thread」</x:v>
+      </x:c>
       <x:c r="K4" s="47" t="str">
         <x:v>已确认三组双控和入户照明总控均为实体有线控制</x:v>
       </x:c>
@@ -1017,27 +1027,31 @@
         <x:v>yes</x:v>
       </x:c>
       <x:c r="E5" s="47" t="str">
-        <x:v>主卧门口控制面板最终墙侧</x:v>
+        <x:v>主卧内 Master A 与主卧入口外 Master B 的真实墙侧分别在哪里</x:v>
       </x:c>
       <x:c r="F5" s="48" t="str">
-        <x:v>Master A</x:v>
+        <x:v>Master A 位于主卧内门后贴墙侧并控制主卧氛围/重点照明；Master B 位于主卧入口外并控制客厅/书房/餐厅三组双控；两处均待 A-104 关闭真实墙侧</x:v>
       </x:c>
       <x:c r="G5" s="49" t="str">
-        <x:v>Master A</x:v>
-      </x:c>
-      <x:c r="H5" s="47" t="str"/>
+        <x:v>Master A，控制主卧氛围照明和重点照明的按钮，在主卧内，不是控制外部客厅书房餐厅的
+PS: 这款也不错，考虑到开关要安装到衣柜的见光板上</x:v>
+      </x:c>
+      <x:c r="H5" s="47"/>
       <x:c r="I5" s="49" t="str">
         <x:v>需证据</x:v>
       </x:c>
-      <x:c r="J5" s="49" t="str"/>
+      <x:c r="J5" s="49" t="str">
+        <x:v>【淘宝】假一赔四 https://e.tb.cn/h.87aqXDS1nDac9bu?tk=4YpQTa7crQs CZ005 「JINK Switch 2.5DNeo Matter墙壁开关欧规英规通用苹果玻璃开关」
+点击链接直接打开 或者 淘宝搜索直接打开</x:v>
+      </x:c>
       <x:c r="K5" s="47" t="str">
-        <x:v>用户明确 Master A 更好；仍依赖 A104-M07-EVIDENCE</x:v>
+        <x:v>用户已明确 Master A 在主卧内、Master B 在主卧入口外，两者不是二选一；当前 IFC 的 M07 仍缺少可靠开启方向证据</x:v>
       </x:c>
       <x:c r="L5" s="47" t="str">
-        <x:v>E302 master control</x:v>
+        <x:v>E302 master control;A104-R03</x:v>
       </x:c>
       <x:c r="M5" s="47" t="str">
-        <x:v>证据关闭后才可冻结</x:v>
+        <x:v>A-104 取证后分别冻结两块面板墙侧、门套净距和见光板安装条件</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="54" customHeight="1">
@@ -1054,25 +1068,27 @@
         <x:v>yes</x:v>
       </x:c>
       <x:c r="E6" s="47" t="str">
-        <x:v>主卧门口面板具体键序</x:v>
+        <x:v>Master A 与 Master B 分别包含哪些键以及采用何种键序</x:v>
       </x:c>
       <x:c r="F6" s="48" t="str">
-        <x:v>客厅双控；书房双控；餐厅双控，常用键靠近门侧</x:v>
-      </x:c>
-      <x:c r="G6" s="49" t="str"/>
-      <x:c r="H6" s="47" t="str"/>
+        <x:v>Master A：主卧氛围照明、主卧重点照明；Master B：客厅双控、书房双控、餐厅双控；常用键靠近门侧</x:v>
+      </x:c>
+      <x:c r="G6" s="49" t="str">
+        <x:v>我转念一想客厅双控；书房双控；餐厅双控需要安装在Master B，是在主卧入口，但不在主卧空间</x:v>
+      </x:c>
+      <x:c r="H6" s="47"/>
       <x:c r="I6" s="49" t="str">
         <x:v>待填写</x:v>
       </x:c>
-      <x:c r="J6" s="49" t="str"/>
+      <x:c r="J6" s="49"/>
       <x:c r="K6" s="47" t="str">
-        <x:v>已确认三组双控需求但每键标签和键序未关闭</x:v>
+        <x:v>用户已明确主卧内照明控制与客厅/书房/餐厅三组双控分别由 Master A、Master B 承担</x:v>
       </x:c>
       <x:c r="L6" s="47" t="str">
-        <x:v>E302 master panel</x:v>
+        <x:v>E302 master panels</x:v>
       </x:c>
       <x:c r="M6" s="47" t="str">
-        <x:v>面板底边候选为完成地面上 1300 mm</x:v>
+        <x:v>面板底边候选为完成地面上 1300 mm；最终键序和产品模数仍待关闭</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="54" customHeight="1">
@@ -1092,16 +1108,23 @@
         <x:v>岛台 NS-01 采用何种插座型式及安装面</x:v>
       </x:c>
       <x:c r="F7" s="48" t="str">
-        <x:v>岛台端板固定插座；避免台面弹起式；根据实际同时使用负荷决定 10A/16A 与孔位数</x:v>
-      </x:c>
-      <x:c r="G7" s="49" t="str"/>
-      <x:c r="H7" s="47" t="str"/>
+        <x:v>岛台 countertop 与桌面 overlap 下方的三个面各设 1 个隐藏盖板式插座位；银色五孔滑盖产品为选型方向；最终按 VVD 详图确认开孔和安装面</x:v>
+      </x:c>
+      <x:c r="G7" s="49" t="str">
+        <x:v>VVD岛台下方就有插座位，在countertop与桌面overlap的位置下方，默认是隐藏面板式的插座。三个面每个面各一个</x:v>
+      </x:c>
+      <x:c r="H7" s="47"/>
       <x:c r="I7" s="49" t="str">
         <x:v>待填写</x:v>
       </x:c>
-      <x:c r="J7" s="49" t="str"/>
+      <x:c r="J7" s="49" t="str">
+        <x:v>/Users/jiaxinchen/Downloads/Deco DL/Molteni&amp;C/VVD/dwg-2d-vvd-showroom-drawing.dwg
+【淘宝】大促价保 https://e.tb.cn/h.87ZCCiBFxejNblD?tk=1aPCTai8okP CA381 「施耐德官方旗舰店滑盖式地插五孔插座面板家用地板六类电脑插座」
+点击链接直接打开 或者 淘宝搜索直接打开
+选用银色5孔地插，这样有个盖子美观</x:v>
+      </x:c>
       <x:c r="K7" s="47" t="str">
-        <x:v>用户明确用于火锅/搅拌机/sous-vide 等移动厨电</x:v>
+        <x:v>用户在 Google Sheet 明确 VVD 岛台下方已有插座位且三个面每面各一个；脚本区分全部列出设备连接包络 2.6–4.9kW 与火锅加搅拌机或 sous-vide 同时包络 1.8–3.7kW</x:v>
       </x:c>
       <x:c r="L7" s="47" t="str">
         <x:v>E303 NS-01</x:v>
@@ -1127,16 +1150,18 @@
         <x:v>岛台移动厨电是否允许同时使用</x:v>
       </x:c>
       <x:c r="F8" s="48" t="str">
-        <x:v>默认按火锅与一件小厨电可能同时使用；若总功率超过单回路容量则拆分回路</x:v>
-      </x:c>
-      <x:c r="G8" s="49" t="str"/>
-      <x:c r="H8" s="47" t="str"/>
+        <x:v>按用户确认的火锅加一件小厨电同时使用核算；2 个独立插座回路作为容量候选并将火锅与其余移动厨电分开；最终按铭牌复核</x:v>
+      </x:c>
+      <x:c r="G8" s="49" t="str">
+        <x:v>同意按火锅与一件小厨电可能同时使用；</x:v>
+      </x:c>
+      <x:c r="H8" s="47"/>
       <x:c r="I8" s="49" t="str">
         <x:v>待填写</x:v>
       </x:c>
-      <x:c r="J8" s="49" t="str"/>
+      <x:c r="J8" s="49"/>
       <x:c r="K8" s="47" t="str">
-        <x:v>使用场景已确认但设备型号和额定功率未提供</x:v>
+        <x:v>同时使用包络约 1.8–3.7kW；上限略高于单个 220V/16A-class 插座规划容量；不据此自动确定线径、保护器或 RCD</x:v>
       </x:c>
       <x:c r="L8" s="47" t="str">
         <x:v>E303 NS-01 load</x:v>
@@ -1162,16 +1187,20 @@
         <x:v>餐边柜 NS-02 插座数量与安装型式</x:v>
       </x:c>
       <x:c r="F9" s="48" t="str">
-        <x:v>咖啡机/手冲壶/磨豆机三设备位；固定墙面或柜上方插座并预留至少一个备用位</x:v>
-      </x:c>
-      <x:c r="G9" s="49" t="str"/>
-      <x:c r="H9" s="47" t="str"/>
+        <x:v>极简线性轨道插座或自制隐藏翻盖作为两种选型方向；至少满足咖啡机、手冲壶和磨豆机三个连接需求；最终按餐边柜立面关闭</x:v>
+      </x:c>
+      <x:c r="G9" s="49" t="str">
+        <x:v>要么是这种极简的线性插座，要么是自制翻盖</x:v>
+      </x:c>
+      <x:c r="H9" s="47"/>
       <x:c r="I9" s="49" t="str">
         <x:v>待填写</x:v>
       </x:c>
-      <x:c r="J9" s="49" t="str"/>
+      <x:c r="J9" s="49" t="str">
+        <x:v>【淘宝】7天无理由退货 https://e.tb.cn/h.870VzbZFjDRIqEn?tk=ySVHTair9B8 CZ001 「XPOWER滑轨插座线性导轨道插排厨房超薄隐藏式隐形内嵌入式多功能」</x:v>
+      </x:c>
       <x:c r="K9" s="47" t="str">
-        <x:v>用户明确实际使用场景为咖啡机/手冲壶/磨豆机</x:v>
+        <x:v>用户在 Google Sheet 明确要么极简线性插座要么自制翻盖；实际使用场景为咖啡机/手冲壶/磨豆机；全部列出设备连接包络 2.35–4.0kW</x:v>
       </x:c>
       <x:c r="L9" s="47" t="str">
         <x:v>E303 NS-02</x:v>
@@ -1197,16 +1226,21 @@
         <x:v>咖啡机与电热水壶是否会同时使用</x:v>
       </x:c>
       <x:c r="F10" s="48" t="str">
-        <x:v>默认按可能同时使用核算；以铭牌功率决定一回路或分回路</x:v>
-      </x:c>
-      <x:c r="G10" s="49" t="str"/>
-      <x:c r="H10" s="47" t="str"/>
+        <x:v>按用户确认咖啡机与手冲壶不会同时使用核算；磨豆机可与咖啡机同用；1 个回路作为容量候选；最终按产品铭牌复核</x:v>
+      </x:c>
+      <x:c r="G10" s="49" t="str">
+        <x:v>不会，咖啡机是喝拿铁的。手冲壶是喝pour over的</x:v>
+      </x:c>
+      <x:c r="H10" s="47"/>
       <x:c r="I10" s="49" t="str">
         <x:v>待填写</x:v>
       </x:c>
-      <x:c r="J10" s="49" t="str"/>
+      <x:c r="J10" s="49" t="str">
+        <x:v>hario手冲壶都行1200W
+咖啡机是lamarzocco 推荐GS3。或者黑鹰Victoria Arduino</x:v>
+      </x:c>
       <x:c r="K10" s="47" t="str">
-        <x:v>咖啡设备存放位置不等于实际使用位置</x:v>
+        <x:v>同时使用包络约 1.0–2.2kW；低于单个 220V/16A-class 插座规划容量；不据此自动确定线径、保护器或 RCD</x:v>
       </x:c>
       <x:c r="L10" s="47" t="str">
         <x:v>E303 NS-02 load</x:v>
@@ -1234,12 +1268,17 @@
       <x:c r="F11" s="48" t="str">
         <x:v>拍摄设备底部铭牌；分别确认光猫/路由器/AP/运营商网关角色</x:v>
       </x:c>
-      <x:c r="G11" s="49" t="str"/>
-      <x:c r="H11" s="47" t="str"/>
+      <x:c r="G11" s="49" t="str">
+        <x:v>这个无所谓的，我自己买个能塞进去的就行。现在是V175+卧室的K155。我肯定要根据AP来决定买哪款</x:v>
+      </x:c>
+      <x:c r="H11" s="47"/>
       <x:c r="I11" s="49" t="str">
         <x:v>需证据</x:v>
       </x:c>
-      <x:c r="J11" s="49" t="str"/>
+      <x:c r="J11" s="49" t="str">
+        <x:v>【淘宝】7天无理由退货 https://e.tb.cn/h.870CJ6ZBs0WvR2W?tk=v0vCTaRQytp HU926 「华为FTTR全光组网青春版V175/K155/K155-11智能组网WIFI6+3000M」
+点击链接直接打开 或者 淘宝搜索直接打开</x:v>
+      </x:c>
       <x:c r="K11" s="47" t="str">
         <x:v>现场照片只证明现有 Huawei 联通智家设备在箱内运行</x:v>
       </x:c>
@@ -1269,14 +1308,18 @@
       <x:c r="F12" s="48" t="str">
         <x:v>现场实测三向净尺寸</x:v>
       </x:c>
-      <x:c r="G12" s="49" t="str"/>
+      <x:c r="G12" s="49" t="str">
+        <x:v>深110x长350x高260，离入户墙：45+400+80=525m</x:v>
+      </x:c>
       <x:c r="H12" s="47" t="str">
         <x:v>mm</x:v>
       </x:c>
       <x:c r="I12" s="49" t="str">
         <x:v>待填写</x:v>
       </x:c>
-      <x:c r="J12" s="49" t="str"/>
+      <x:c r="J12" s="49" t="str">
+        <x:v>https://app.notion.com/p/weihanshen/3b9fda08ab6c805bbc4bef80fa997bc4?source=copy_link</x:v>
+      </x:c>
       <x:c r="K12" s="47" t="str">
         <x:v>官方 CAD 和现场照片已确认位置但没有净尺寸</x:v>
       </x:c>
@@ -1306,14 +1349,16 @@
       <x:c r="F13" s="48" t="str">
         <x:v>关闭柜门运行 2 小时后记录箱内或设备表面温度；拍摄通风条件</x:v>
       </x:c>
-      <x:c r="G13" s="49" t="str"/>
+      <x:c r="G13" s="49" t="str">
+        <x:v>弱电箱盖板上有通风孔，温度摸起来正常，30-40度</x:v>
+      </x:c>
       <x:c r="H13" s="47" t="str">
         <x:v>°C</x:v>
       </x:c>
       <x:c r="I13" s="49" t="str">
         <x:v>待填写</x:v>
       </x:c>
-      <x:c r="J13" s="49" t="str"/>
+      <x:c r="J13" s="49"/>
       <x:c r="K13" s="47" t="str">
         <x:v>现有设备实际在弱电箱内部运行</x:v>
       </x:c>
@@ -1343,12 +1388,14 @@
       <x:c r="F14" s="48" t="str">
         <x:v>逐根用测线仪确认客厅/次卧/主卧并记录两端标签</x:v>
       </x:c>
-      <x:c r="G14" s="49" t="str"/>
-      <x:c r="H14" s="47" t="str"/>
+      <x:c r="G14" s="49" t="str">
+        <x:v>主卧次卧客厅（旋转180度查看图片）</x:v>
+      </x:c>
+      <x:c r="H14" s="47"/>
       <x:c r="I14" s="49" t="str">
         <x:v>待填写</x:v>
       </x:c>
-      <x:c r="J14" s="49" t="str"/>
+      <x:c r="J14" s="49"/>
       <x:c r="K14" s="47" t="str">
         <x:v>照片标签只是候选不能替代通断测试</x:v>
       </x:c>
@@ -1376,22 +1423,24 @@
         <x:v>主卧和次卧 AP 采用 PoE 还是本地电源</x:v>
       </x:c>
       <x:c r="F15" s="48" t="str">
-        <x:v>PoE 优先；弱电箱设置 PoE 交换机或 PoE 路由端口</x:v>
-      </x:c>
-      <x:c r="G15" s="49" t="str"/>
-      <x:c r="H15" s="47" t="str"/>
+        <x:v>按最终 AP 型号二选一：PoE 时弱电箱配置兼容供电端口并校核功率预算；本地电源时在隐蔽吊顶检修范围内预留可维护电源</x:v>
+      </x:c>
+      <x:c r="G15" s="49" t="str">
+        <x:v>我不知道，PoE是什么意思。目前的K155是有电源的。我们要隐蔽安装，天花内估计要预留电源</x:v>
+      </x:c>
+      <x:c r="H15" s="47"/>
       <x:c r="I15" s="49" t="str">
         <x:v>待填写</x:v>
       </x:c>
-      <x:c r="J15" s="49" t="str"/>
+      <x:c r="J15" s="49"/>
       <x:c r="K15" s="47" t="str">
-        <x:v>卧室 AP 点位已有平面/标高候选但供电方式未关闭</x:v>
+        <x:v>用户说明现有 K155 使用本地电源；卧室 AP 点位已有平面/标高候选但最终设备和供电方式未关闭</x:v>
       </x:c>
       <x:c r="L15" s="47" t="str">
         <x:v>E304 AP topology</x:v>
       </x:c>
       <x:c r="M15" s="47" t="str">
-        <x:v>最终取决于 AP 产品型号</x:v>
+        <x:v>不得在 AP 型号确定前把 PoE 或本地电源写成最终方案</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="54" customHeight="1">
@@ -1413,12 +1462,14 @@
       <x:c r="F16" s="48" t="str">
         <x:v>厨房油烟环境下感温优先作为协调候选；最终由消防/设备方确认</x:v>
       </x:c>
-      <x:c r="G16" s="49" t="str"/>
-      <x:c r="H16" s="47" t="str"/>
+      <x:c r="G16" s="49" t="str">
+        <x:v>泛海三江温感JTW-ZD-920A20复合式感烟感温火灾探测器</x:v>
+      </x:c>
+      <x:c r="H16" s="47"/>
       <x:c r="I16" s="49" t="str">
         <x:v>需证据</x:v>
       </x:c>
-      <x:c r="J16" s="49" t="str"/>
+      <x:c r="J16" s="49"/>
       <x:c r="K16" s="47" t="str">
         <x:v>正式 IFC 只确认 IfcSensor/FIRESENSOR 点位未确认产品</x:v>
       </x:c>
@@ -1448,12 +1499,14 @@
       <x:c r="F17" s="48" t="str">
         <x:v>先向燃气公司确认允许型号与距灶具/阀门/顶棚要求</x:v>
       </x:c>
-      <x:c r="G17" s="49" t="str"/>
-      <x:c r="H17" s="47" t="str"/>
+      <x:c r="G17" s="49" t="str">
+        <x:v>燃气报警器JT-GS838C-NBAC-H05移动</x:v>
+      </x:c>
+      <x:c r="H17" s="47"/>
       <x:c r="I17" s="49" t="str">
         <x:v>需证据</x:v>
       </x:c>
-      <x:c r="J17" s="49" t="str"/>
+      <x:c r="J17" s="49"/>
       <x:c r="K17" s="47" t="str">
         <x:v>当前只有需求和候选包络</x:v>
       </x:c>
@@ -1483,14 +1536,16 @@
       <x:c r="F18" s="48" t="str">
         <x:v>耐擦洗哑光乳胶漆体系作为比较候选，不代表选定产品</x:v>
       </x:c>
-      <x:c r="G18" s="49" t="str"/>
+      <x:c r="G18" s="49" t="str">
+        <x:v>谢柯大白墙，全生堂，1mm?</x:v>
+      </x:c>
       <x:c r="H18" s="47" t="str">
         <x:v>mm</x:v>
       </x:c>
       <x:c r="I18" s="49" t="str">
         <x:v>暂缓</x:v>
       </x:c>
-      <x:c r="J18" s="49" t="str"/>
+      <x:c r="J18" s="49"/>
       <x:c r="K18" s="47" t="str">
         <x:v>用户要求统一选材时处理</x:v>
       </x:c>
@@ -1520,14 +1575,16 @@
       <x:c r="F19" s="48" t="str">
         <x:v>以完整厂家系统和湿区节点样板为选择条件</x:v>
       </x:c>
-      <x:c r="G19" s="49" t="str"/>
+      <x:c r="G19" s="49" t="str">
+        <x:v>https://www.modamuri.com/sqztdl.html</x:v>
+      </x:c>
       <x:c r="H19" s="47" t="str">
         <x:v>mm</x:v>
       </x:c>
       <x:c r="I19" s="49" t="str">
         <x:v>暂缓</x:v>
       </x:c>
-      <x:c r="J19" s="49" t="str"/>
+      <x:c r="J19" s="49"/>
       <x:c r="K19" s="47" t="str">
         <x:v>当前仅确认材料意图未确认产品体系</x:v>
       </x:c>
@@ -1557,12 +1614,14 @@
       <x:c r="F20" s="48" t="str">
         <x:v>厂家安装图或 BIM/DWG 接口图</x:v>
       </x:c>
-      <x:c r="G20" s="49" t="str"/>
-      <x:c r="H20" s="47" t="str"/>
+      <x:c r="G20" s="49" t="str">
+        <x:v>你表里没给我型号</x:v>
+      </x:c>
+      <x:c r="H20" s="47"/>
       <x:c r="I20" s="49" t="str">
-        <x:v>需证据</x:v>
-      </x:c>
-      <x:c r="J20" s="49" t="str"/>
+        <x:v>待填写</x:v>
+      </x:c>
+      <x:c r="J20" s="49"/>
       <x:c r="K20" s="47" t="str">
         <x:v>机位和路线骨架已确认但精确端口坐标尚无批准证据</x:v>
       </x:c>
@@ -1592,12 +1651,14 @@
       <x:c r="F21" s="48" t="str">
         <x:v>按最终产品逐台收集安装图；存放位置不得代替使用和接口位置</x:v>
       </x:c>
-      <x:c r="G21" s="49" t="str"/>
-      <x:c r="H21" s="47" t="str"/>
+      <x:c r="G21" s="49" t="str">
+        <x:v>写不下</x:v>
+      </x:c>
+      <x:c r="H21" s="47"/>
       <x:c r="I21" s="49" t="str">
         <x:v>需证据</x:v>
       </x:c>
-      <x:c r="J21" s="49" t="str"/>
+      <x:c r="J21" s="49"/>
       <x:c r="K21" s="47" t="str">
         <x:v>现有模型端点不是正式 IfcDistributionPort</x:v>
       </x:c>
@@ -1627,14 +1688,14 @@
       <x:c r="F22" s="48" t="str">
         <x:v>优先采用完整厂家体系并与地漏坡向/门槛高差一起审核</x:v>
       </x:c>
-      <x:c r="G22" s="49" t="str"/>
+      <x:c r="G22" s="49"/>
       <x:c r="H22" s="47" t="str">
         <x:v>mm</x:v>
       </x:c>
       <x:c r="I22" s="49" t="str">
         <x:v>待填写</x:v>
       </x:c>
-      <x:c r="J22" s="49" t="str"/>
+      <x:c r="J22" s="49"/>
       <x:c r="K22" s="47" t="str">
         <x:v>DET1 尚未开始且依赖 WFIN/A105/INT1</x:v>
       </x:c>
@@ -1658,7 +1719,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24ba38ab136f4d68"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06f52f7e542e461c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2239,14 +2300,18 @@
       <x:c r="E12" s="48" t="str">
         <x:v>西厨高柜</x:v>
       </x:c>
-      <x:c r="F12" s="49" t="str"/>
+      <x:c r="F12" s="49" t="str">
+        <x:v>西厨高柜</x:v>
+      </x:c>
       <x:c r="G12" s="49" t="str">
         <x:v>西厨高柜</x:v>
       </x:c>
-      <x:c r="H12" s="49" t="str">
+      <x:c r="H12" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I12" s="49" t="str"/>
+      <x:c r="I12" s="49" t="n">
+        <x:v>3400</x:v>
+      </x:c>
       <x:c r="J12" s="49" t="str">
         <x:v>COOKING-A</x:v>
       </x:c>
@@ -2260,15 +2325,19 @@
         <x:v>no</x:v>
       </x:c>
       <x:c r="N12" s="49" t="str">
-        <x:v>model_dependent</x:v>
-      </x:c>
-      <x:c r="O12" s="49" t="str"/>
-      <x:c r="P12" s="49" t="str"/>
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="O12" s="49" t="str">
+        <x:v>Siemens HB754G2B1W</x:v>
+      </x:c>
+      <x:c r="P12" s="49" t="str">
+        <x:v>APP-011-PHOTO-001;APP-011-OFFICIAL-001</x:v>
+      </x:c>
       <x:c r="Q12" s="49" t="str">
-        <x:v>待填写</x:v>
+        <x:v>已确认</x:v>
       </x:c>
       <x:c r="R12" s="49" t="str">
-        <x:v>补额定功率和散热要求</x:v>
+        <x:v>已到货（包装照片）；220V/50Hz，最大功率3400W，16A插头；机身595×594×548 mm；柜体开口宽560–568、高585–595、深≥550 mm；进风面积≥200 cm²；电源线约1.2 m。</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="42" customHeight="1">
@@ -2287,14 +2356,18 @@
       <x:c r="E13" s="48" t="str">
         <x:v>中厨</x:v>
       </x:c>
-      <x:c r="F13" s="49" t="str"/>
+      <x:c r="F13" s="49" t="str">
+        <x:v>中厨</x:v>
+      </x:c>
       <x:c r="G13" s="49" t="str">
         <x:v>中厨</x:v>
       </x:c>
-      <x:c r="H13" s="49" t="str">
+      <x:c r="H13" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I13" s="49" t="str"/>
+      <x:c r="I13" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J13" s="49" t="str">
         <x:v>COOKING-B</x:v>
       </x:c>
@@ -2305,18 +2378,22 @@
         <x:v>no</x:v>
       </x:c>
       <x:c r="M13" s="49" t="str">
-        <x:v>model_dependent</x:v>
+        <x:v>yes</x:v>
       </x:c>
       <x:c r="N13" s="49" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="O13" s="49" t="str"/>
-      <x:c r="P13" s="49" t="str"/>
+      <x:c r="O13" s="49" t="str">
+        <x:v>Siemens ER9EPA33MP/01（JZT-ER9EPA33MP）</x:v>
+      </x:c>
+      <x:c r="P13" s="49" t="str">
+        <x:v>APP-012-PHOTO-001;APP-012-PHOTO-002;APP-012-OFFICIAL-001</x:v>
+      </x:c>
       <x:c r="Q13" s="49" t="str">
-        <x:v>待填写</x:v>
+        <x:v>已确认</x:v>
       </x:c>
       <x:c r="R13" s="49" t="str">
-        <x:v>确认燃气或电气类型</x:v>
+        <x:v>已到货（包装照片）；天然气12T/2.0kPa；额定热负荷左/中/右5.2/2.0/5.2kW；DC1.5V电池点火；外形920×500×150 mm；台面开孔880×455 mm、4×R15；橱柜通风≥100cm²；独立安装下方净空≥100mm（下置电器时隔板至台面≥120mm）；燃气接驳以当地燃气公司要求为准。</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="42" customHeight="1">
@@ -2335,14 +2412,18 @@
       <x:c r="E14" s="48" t="str">
         <x:v>中厨</x:v>
       </x:c>
-      <x:c r="F14" s="49" t="str"/>
+      <x:c r="F14" s="49" t="str">
+        <x:v>中厨</x:v>
+      </x:c>
       <x:c r="G14" s="49" t="str">
         <x:v>中厨</x:v>
       </x:c>
-      <x:c r="H14" s="49" t="str">
+      <x:c r="H14" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I14" s="49" t="str"/>
+      <x:c r="I14" s="49" t="n">
+        <x:v>385</x:v>
+      </x:c>
       <x:c r="J14" s="49" t="str">
         <x:v>COOKING-B</x:v>
       </x:c>
@@ -2358,13 +2439,17 @@
       <x:c r="N14" s="49" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="O14" s="49" t="str"/>
-      <x:c r="P14" s="49" t="str"/>
+      <x:c r="O14" s="49" t="str">
+        <x:v>Siemens LS33R6VB9W/01（CXW-380-LS33R6VB9W）</x:v>
+      </x:c>
+      <x:c r="P14" s="49" t="str">
+        <x:v>APP-013-PHOTO-001;APP-013-PHOTO-002;APP-013-OFFICIAL-001</x:v>
+      </x:c>
       <x:c r="Q14" s="49" t="str">
-        <x:v>待填写</x:v>
+        <x:v>已确认</x:v>
       </x:c>
       <x:c r="R14" s="49" t="str">
-        <x:v>补功率/排烟接口/止回阀资料</x:v>
+        <x:v>已到货（包装照片）；220V/50Hz，额定输入385W；外形895×345×873 mm；烟管及止逆阀内径≥160mm，烟管宜≤3m且1弯；墙洞建议Ø180mm；吊顶圆孔Ø190mm；吊顶内预留电源；检修口建议400×400mm；与燃气灶承锅面净距≥650mm；电源线约1.3m。</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="42" customHeight="1">
@@ -2631,7 +2716,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd1aeb77ac9c4b72"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb53985debee448c2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/output/forms/滨海湾施工输入清单.xlsx
+++ b/output/forms/滨海湾施工输入清单.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="R40e2ddf5d920432f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计决策" sheetId="2" r:id="R0a1a5f63e7284778"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="家电清单" sheetId="3" r:id="Rfc8eb7af8b0a4863"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="Rd1154c5b447947ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计决策" sheetId="2" r:id="Rab8c3551ba004ea6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="家电清单" sheetId="3" r:id="R6d98dfcc9fe54186"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1001,16 +1001,20 @@
         <x:v>待填写</x:v>
       </x:c>
       <x:c r="J4" s="49" t="str">
-        <x:v>【淘宝】假一赔四 https://e.tb.cn/h.87aSpFYZgStgIgK?tk=DBrSTaSu8bF CZ057 「JINK Switch EGG智能墙壁开关场景EGG直连全屋智能家居Thread」</x:v>
+        <x:v>【淘宝】假一赔四 https://e.tb.cn/h.87aSpFYZgStgIgK?tk=DBrSTaSu8bF CZ057 「JINK Switch EGG智能墙壁开关场景EGG直连全屋智能家居Thread」
+CSA JINK 8e: https://csa-iot.org/csa_product/jink-8e-switch-series-6/
+Apple Matter: https://support.apple.com/en-ie/102135
+Google Matter: https://support.google.com/googlehome/answer/12391458?hl=en
+KNX position: https://knx.org/news/knx-and-matter-position-paper</x:v>
       </x:c>
       <x:c r="K4" s="47" t="str">
-        <x:v>已确认三组双控和入户照明总控均为实体有线控制</x:v>
+        <x:v>CSA 官方库确认 Longan Link 的 JINK 8e 系列存在 Matter 1.1、Thread + Bluetooth 认证；Apple 和 Google 官方均支持 Matter 多生态控制；KNX 官方将 Matter 视为可结合但不同的体系</x:v>
       </x:c>
       <x:c r="L4" s="47" t="str">
         <x:v>E302 entry panel</x:v>
       </x:c>
       <x:c r="M4" s="47" t="str">
-        <x:v>总控不得切断冰箱/网络/安防等持续供电</x:v>
+        <x:v>Matter 不是 KNX；Android 与 Apple 均可通过相应 Matter 平台控制；Thread 设备需 Thread Border Router。淘宝 EGG 具体 SKU 尚未对应到 CSA Family SKU，且负载类型、零火线、面板模数和接线图未核实，不得选定</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="54" customHeight="1">
@@ -1719,7 +1723,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06f52f7e542e461c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea077b4266d94a1a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2716,7 +2720,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb53985debee448c2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c4c28d520c0465f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/output/forms/滨海湾施工输入清单.xlsx
+++ b/output/forms/滨海湾施工输入清单.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="Rd1154c5b447947ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计决策" sheetId="2" r:id="Rab8c3551ba004ea6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="家电清单" sheetId="3" r:id="R6d98dfcc9fe54186"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="R6ce0b3876043499a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计决策" sheetId="2" r:id="Rfd27d1dfa4c14c9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="家电清单" sheetId="3" r:id="R03320a601bf04dae"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -788,7 +788,7 @@
       </x:c>
       <x:c r="B14" s="37" t="n">
         <x:f>COUNTIFS('设计决策'!D2:D22,"yes",'设计决策'!I2:I22,"&lt;&gt;采用候选",'设计决策'!I2:I22,"&lt;&gt;自定义确认",'设计决策'!I2:I22,"&lt;&gt;不适用")</x:f>
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C14" s="26"/>
       <x:c r="D14" s="26"/>
@@ -1119,7 +1119,7 @@
       </x:c>
       <x:c r="H7" s="47"/>
       <x:c r="I7" s="49" t="str">
-        <x:v>待填写</x:v>
+        <x:v>采用候选</x:v>
       </x:c>
       <x:c r="J7" s="49" t="str">
         <x:v>/Users/jiaxinchen/Downloads/Deco DL/Molteni&amp;C/VVD/dwg-2d-vvd-showroom-drawing.dwg
@@ -1161,7 +1161,7 @@
       </x:c>
       <x:c r="H8" s="47"/>
       <x:c r="I8" s="49" t="str">
-        <x:v>待填写</x:v>
+        <x:v>采用候选</x:v>
       </x:c>
       <x:c r="J8" s="49"/>
       <x:c r="K8" s="47" t="str">
@@ -1237,7 +1237,7 @@
       </x:c>
       <x:c r="H10" s="47"/>
       <x:c r="I10" s="49" t="str">
-        <x:v>待填写</x:v>
+        <x:v>采用候选</x:v>
       </x:c>
       <x:c r="J10" s="49" t="str">
         <x:v>hario手冲壶都行1200W
@@ -1473,15 +1473,17 @@
       <x:c r="I16" s="49" t="str">
         <x:v>需证据</x:v>
       </x:c>
-      <x:c r="J16" s="49"/>
+      <x:c r="J16" s="49" t="str">
+        <x:v>A106-FIRE-OFFICIAL-001;A106-FIRE-OFFICIAL-002;A106-FIRE-OFFICIAL-003</x:v>
+      </x:c>
       <x:c r="K16" s="47" t="str">
-        <x:v>正式 IFC 只确认 IfcSensor/FIRESENSOR 点位未确认产品</x:v>
+        <x:v>厂家官方资料分别证明 JTW-ZD-A20 与 JTW-ZD-920E 是感温型，复合式使用独立型号 JTF-GDM-936；用户文本无法匹配为一个官方产品</x:v>
       </x:c>
       <x:c r="L16" s="47" t="str">
         <x:v>A106-FIRE-R04</x:v>
       </x:c>
       <x:c r="M16" s="47" t="str">
-        <x:v>不得把候选类型或尺寸写成正式产品</x:v>
+        <x:v>正式 IFC 只保留已确认 IfcSensor/FIRESENSOR 点位；不得把拼接型号、复合身份或候选尺寸写成正式产品</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="54" customHeight="1">
@@ -1510,15 +1512,17 @@
       <x:c r="I17" s="49" t="str">
         <x:v>需证据</x:v>
       </x:c>
-      <x:c r="J17" s="49"/>
+      <x:c r="J17" s="49" t="str">
+        <x:v>A106-GAS-OFFICIAL-001</x:v>
+      </x:c>
       <x:c r="K17" s="47" t="str">
-        <x:v>当前只有需求和候选包络</x:v>
+        <x:v>厂家官方页面只证明 JT-GS838 系列的家用甲烷探测器属性；未匹配精确后缀 C-NBAC-H05 及其当前认证</x:v>
       </x:c>
       <x:c r="L17" s="47" t="str">
         <x:v>A106 gas alarm</x:v>
       </x:c>
       <x:c r="M17" s="47" t="str">
-        <x:v>型号确认前不得锁定开孔</x:v>
+        <x:v>精确型号、燃气公司准入、施工距离和官方说明书关闭前不得锁定开孔或供电通信方案</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="54" customHeight="1">
@@ -1723,7 +1727,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea077b4266d94a1a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb20d0205b45f406f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1901,7 +1905,7 @@
         <x:v>部分确认</x:v>
       </x:c>
       <x:c r="R3" s="49" t="str">
-        <x:v>与火锅是否同时使用待确认</x:v>
+        <x:v>用户已确认可与火锅同时使用；仍缺型号与铭牌功率</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="42" customHeight="1">
@@ -2045,7 +2049,7 @@
         <x:v>部分确认</x:v>
       </x:c>
       <x:c r="R6" s="49" t="str">
-        <x:v>按可能与咖啡机同时使用核算</x:v>
+        <x:v>用户已确认不与咖啡机同时使用；仍缺最终型号与铭牌功率</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="42" customHeight="1">
@@ -2720,7 +2724,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c4c28d520c0465f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23cd8901f028479a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/output/forms/滨海湾施工输入清单.xlsx
+++ b/output/forms/滨海湾施工输入清单.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="R6ce0b3876043499a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计决策" sheetId="2" r:id="Rfd27d1dfa4c14c9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="家电清单" sheetId="3" r:id="R03320a601bf04dae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="R20aa4fa19aed4f9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计决策" sheetId="2" r:id="Rbf9262680b3e4b61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="家电清单" sheetId="3" r:id="R3ca2a277314e4098"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -923,9 +923,9 @@
         <x:v>需证据</x:v>
       </x:c>
       <x:c r="J2" s="49" t="str">
-        <x:v>https://s3.poliform.it/2025/04/Poliform_Architectural_2024.pdf
-freestanding wardrobe and wall mounted Pivot
-</x:v>
+        <x:v>https://www.poliform.it/en/products/pivot/
+https://s3.poliform.it/2025/04/Poliform_Architectural_2024.pdf
+Pivot between wardrobe and wall: freestanding wardrobe and wall mounted Pivot</x:v>
       </x:c>
       <x:c r="K2" s="47" t="str">
         <x:v>用户已确认 Master A 更符合实际开门贴墙关系；当前 IFC 无宿主洞口且 OperationType=NOTDEFINED</x:v>
@@ -1727,7 +1727,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb20d0205b45f406f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b710d53dc7f4b21"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2219,7 +2219,9 @@
       <x:c r="H10" s="49" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I10" s="49" t="str"/>
+      <x:c r="I10" s="49" t="n">
+        <x:v>2000</x:v>
+      </x:c>
       <x:c r="J10" s="49" t="str">
         <x:v>DISHWASHER-A</x:v>
       </x:c>
@@ -2235,13 +2237,21 @@
       <x:c r="N10" s="49" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="O10" s="49" t="str"/>
-      <x:c r="P10" s="49" t="str"/>
+      <x:c r="O10" s="49" t="str">
+        <x:v>Siemens SJ85ZX26MC</x:v>
+      </x:c>
+      <x:c r="P10" s="49" t="str">
+        <x:v>【用户选型候选】https://e.tb.cn/h.8TnxVNjugUfIImB?tk=93QITaQnSCj CZ007
+【西门子中国】https://www.siemens-home.bsh-group.com/cn/zh/mkt-product/SJ85ZX26MC
+【官方规格表】drawings/evidence/APP-009-010-Siemens-SJ85ZX26MC-specsheet.pdf
+【官方安装图】drawings/evidence/APP-009-010-Siemens-SJ85ZX26MC-installation-9002067344_A.pdf
+【官方说明书】drawings/evidence/APP-009-010-Siemens-SJ85ZX26MC-user-manual-9002057324_C.pdf</x:v>
+      </x:c>
       <x:c r="Q10" s="49" t="str">
-        <x:v>待填写</x:v>
+        <x:v>部分确认</x:v>
       </x:c>
       <x:c r="R10" s="49" t="str">
-        <x:v>IFC 身份已确认；补产品安装图</x:v>
+        <x:v>Google Sheet 已填写选型候选，尚未采购；官方确认 2000 W/220 V，产品 775×598×550 mm，柜孔 H780–835×W600–608×D≥550 mm，G3/4 冷水、Ø38 排水、管线孔≥100×50 mm，门板 W594、厚≤20 mm、重3.5–8.5 kg。仍须分别核对采购/铭牌 E-Nr. 与 FD、门板高度和踢脚开门关系、现场阀门/排水/插座位置及可抽出检修空间；不得把候选型号写成已购产品。</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="42" customHeight="1">
@@ -2267,7 +2277,9 @@
       <x:c r="H11" s="49" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I11" s="49" t="str"/>
+      <x:c r="I11" s="49" t="n">
+        <x:v>2000</x:v>
+      </x:c>
       <x:c r="J11" s="49" t="str">
         <x:v>DISHWASHER-B</x:v>
       </x:c>
@@ -2283,13 +2295,21 @@
       <x:c r="N11" s="49" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="O11" s="49" t="str"/>
-      <x:c r="P11" s="49" t="str"/>
+      <x:c r="O11" s="49" t="str">
+        <x:v>Siemens SJ85ZX26MC</x:v>
+      </x:c>
+      <x:c r="P11" s="49" t="str">
+        <x:v>【用户选型候选】https://e.tb.cn/h.8TnxVNjugUfIImB?tk=93QITaQnSCj CZ007
+【西门子中国】https://www.siemens-home.bsh-group.com/cn/zh/mkt-product/SJ85ZX26MC
+【官方规格表】drawings/evidence/APP-009-010-Siemens-SJ85ZX26MC-specsheet.pdf
+【官方安装图】drawings/evidence/APP-009-010-Siemens-SJ85ZX26MC-installation-9002067344_A.pdf
+【官方说明书】drawings/evidence/APP-009-010-Siemens-SJ85ZX26MC-user-manual-9002057324_C.pdf</x:v>
+      </x:c>
       <x:c r="Q11" s="49" t="str">
-        <x:v>待填写</x:v>
+        <x:v>部分确认</x:v>
       </x:c>
       <x:c r="R11" s="49" t="str">
-        <x:v>IFC 身份已确认；补产品安装图</x:v>
+        <x:v>Google Sheet 已填写选型候选，尚未采购；官方确认 2000 W/220 V，产品 775×598×550 mm，柜孔 H780–835×W600–608×D≥550 mm，G3/4 冷水、Ø38 排水、管线孔≥100×50 mm，门板 W594、厚≤20 mm、重3.5–8.5 kg。仍须分别核对采购/铭牌 E-Nr. 与 FD、门板高度和踢脚开门关系、现场阀门/排水/插座位置及可抽出检修空间；不得把候选型号写成已购产品。</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="42" customHeight="1">
@@ -2724,7 +2744,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23cd8901f028479a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0becbbab62664930"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/output/forms/滨海湾施工输入清单.xlsx
+++ b/output/forms/滨海湾施工输入清单.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="R2a004f50a8b44903"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计决策" sheetId="2" r:id="Re29768d67edc4918"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="家电清单" sheetId="3" r:id="R1a801910ca644b41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设备主表" sheetId="4" r:id="R32c2abf48f4146df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安装条件" sheetId="5" r:id="R5502d8e5f62c479f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据索引" sheetId="6" r:id="R455c93c844b24a2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="Rcd3a3e1ad65c414d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计决策" sheetId="2" r:id="R9c40856b53ba4d6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="家电清单" sheetId="3" r:id="Rb18319bbec054695"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设备主表" sheetId="4" r:id="R1a1a08d7b5474210"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安装条件" sheetId="5" r:id="Ra225932d122c49bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据索引" sheetId="6" r:id="R659a2fc467a045a7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -298,18 +298,8 @@
     <x:border/>
     <x:border/>
     <x:border/>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
+    <x:border/>
+    <x:border/>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2078,7 +2068,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb52f50ad44f4ad4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12761e58b26d4038"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3015,7 +3005,9 @@
         <x:v>yes</x:v>
       </x:c>
       <x:c r="O18" s="49" t="str"/>
-      <x:c r="P18" s="49" t="str"/>
+      <x:c r="P18" s="49" t="str">
+        <x:v>正式 IFC 的 IfcBuildingElementProxy GlobalId 与既有体量</x:v>
+      </x:c>
       <x:c r="Q18" s="49" t="str">
         <x:v>待填写</x:v>
       </x:c>
@@ -3095,7 +3087,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f736768224b450a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31919d60df034609"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4382,19 +4374,27 @@
         <x:v>yes</x:v>
       </x:c>
       <x:c r="P19" s="108" t="str">
-        <x:v>logical_input</x:v>
+        <x:v>global_id</x:v>
       </x:c>
       <x:c r="Q19" s="108" t="str">
-        <x:v>APP-017</x:v>
-      </x:c>
-      <x:c r="R19" s="108" t="str"/>
+        <x:v>3JAkt8PsX7vPfGKWLK5EKp</x:v>
+      </x:c>
+      <x:c r="R19" s="108" t="str">
+        <x:v>IfcBuildingElementProxy</x:v>
+      </x:c>
       <x:c r="S19" s="108" t="str"/>
       <x:c r="T19" s="108" t="str"/>
-      <x:c r="U19" s="108" t="str"/>
-      <x:c r="V19" s="108" t="str"/>
-      <x:c r="W19" s="108" t="str"/>
+      <x:c r="U19" s="108" t="str">
+        <x:v>3JAkt8PsX7vPfGKWLK5EKp</x:v>
+      </x:c>
+      <x:c r="V19" s="108" t="str">
+        <x:v>IFC-FORMAL-001</x:v>
+      </x:c>
+      <x:c r="W19" s="108" t="str">
+        <x:v>正式 IFC 的 IfcBuildingElementProxy GlobalId 与既有体量</x:v>
+      </x:c>
       <x:c r="X19" s="108" t="str">
-        <x:v>0.80</x:v>
+        <x:v>1.00</x:v>
       </x:c>
       <x:c r="Y19" s="108" t="str">
         <x:v>yes</x:v>
@@ -13631,7 +13631,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ce4cf1cfef545fc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb64d6bafc0b4851"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27345,7 +27345,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R587182e7e0a0464c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14b9dfe2e38c4710"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -33273,7 +33273,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8c1021d5455412d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb45250629854c76"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/output/forms/滨海湾施工输入清单.xlsx
+++ b/output/forms/滨海湾施工输入清单.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="R716cc185b97a4765"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计决策" sheetId="2" r:id="R0a5fca9c609c4d6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="家电清单" sheetId="3" r:id="Reb55ea0f5e7d47c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设备主表" sheetId="4" r:id="R10e2bd6f7d02465c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安装条件" sheetId="5" r:id="R03b70621aa65432e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据索引" sheetId="6" r:id="R2cab1669d3bf4894"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="R44845bddad174f1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计决策" sheetId="2" r:id="R8e80c2bef88e468b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="家电清单" sheetId="3" r:id="Rf3c077dc7e444b5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设备主表" sheetId="4" r:id="R3cc4d9db698e42e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安装条件" sheetId="5" r:id="Rff3c89e8a2824e3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据索引" sheetId="6" r:id="R05359319423040ce"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1127,7 +1127,7 @@
       </x:c>
       <x:c r="B14" s="37" t="n">
         <x:f>COUNTIFS('设计决策'!D2:D24,"yes",'设计决策'!I2:I24,"&lt;&gt;采用候选",'设计决策'!I2:I24,"&lt;&gt;自定义确认",'设计决策'!I2:I24,"&lt;&gt;不适用")</x:f>
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C14" s="26"/>
       <x:c r="D14" s="26"/>
@@ -1294,10 +1294,12 @@
       <x:c r="F2" s="48" t="str">
         <x:v>按 EXISTING/NEW 分组；各组北到南、同排西到东、最后按 GlobalId 稳定排序</x:v>
       </x:c>
-      <x:c r="G2" s="49" t="str"/>
+      <x:c r="G2" s="49" t="str">
+        <x:v>按候选规则直接编号；以后常规编号无需逐项询问，先按稳定可追溯规则生成，后续不满意再改</x:v>
+      </x:c>
       <x:c r="H2" s="47" t="str"/>
       <x:c r="I2" s="49" t="str">
-        <x:v>待填写</x:v>
+        <x:v>自定义确认</x:v>
       </x:c>
       <x:c r="J2" s="49" t="str">
         <x:v>output/images/A-103-wall-tag-review.png;build/a103/a103-wall-tag-candidate.json</x:v>
@@ -1309,7 +1311,7 @@
         <x:v>A103 wall tags;P0 IDS</x:v>
       </x:c>
       <x:c r="M2" s="47" t="str">
-        <x:v>确认后仅写入 88 面最终建成 IfcWall.Tag；不改几何、placement、宿主关系或 M05–M07 尺寸</x:v>
+        <x:v>用户于 2026-08-13 明确批准 A-103 规则并授权今后常规编号自治；仅写入 88 面最终建成 IfcWall.Tag；不改几何、placement、宿主关系或 M05–M07 尺寸；涉及外部合同编号、既有现场标识或回路系统身份时仍须单独核对</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="54" customHeight="1">
@@ -2180,9 +2182,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d0e8529d4e74f1c"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76f673fb1b944aad"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02743a3186c6440c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7cafc5467aa48cb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3201,7 +3203,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf60ac126ebdf4bd3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb05c6e2d7b704c6f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13745,7 +13747,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d3be995382f496b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf35aa1bdc4544e60"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27459,7 +27461,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3fc13b48e404a9d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72856aab7a984670"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -33387,7 +33389,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcaf65b1b3e5742d3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f7bf73b1faa49de"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/output/forms/滨海湾施工输入清单.xlsx
+++ b/output/forms/滨海湾施工输入清单.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="Rabaff23548b4400d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计决策" sheetId="2" r:id="R1b9dfc273c434453"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="家电清单" sheetId="3" r:id="Recd6ad36115b4806"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设备主表" sheetId="4" r:id="Ra5ac116405f94012"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安装条件" sheetId="5" r:id="R54fc7bbade4e4c47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据索引" sheetId="6" r:id="Rb0ba7884a5474fed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="R07463a316a634706"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计决策" sheetId="2" r:id="R85c2ec3b1c5a42e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="家电清单" sheetId="3" r:id="R7af9378b8e5f4626"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设备主表" sheetId="4" r:id="Rea096b0f40d34efb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安装条件" sheetId="5" r:id="R5dfe58e0f18d4f6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据索引" sheetId="6" r:id="Rae501dc2f4f04a32"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2439,9 +2439,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d2bc615c2ce40a8"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc11e66dfec874b97"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d075a84362f4af3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1725b20cbe13445e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3460,7 +3460,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R808fa5355e374cc0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44cea5e9a14043f2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14599,7 +14599,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R768a9660a08a40ed"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra970caf1dd75492d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -35224,7 +35224,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28367aef32f7439b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7fc561ca6d464b05"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43084,13 +43084,13 @@
         <x:v>4eeaeb27b0668bb22b9b4fb191091e07eabbb2b259d90cedcdc45584a1f68e52</x:v>
       </x:c>
       <x:c r="J120" s="132" t="str">
-        <x:v>官方 DWG／AC1024／用户于 2026-08-13 指定</x:v>
+        <x:v>官方 DWG／AC1024；提交的验证转换件 drawings/evidence/RIMADESIO-Sail-monorotaia.dxf；DXF SHA-256 76b40456832e6c3e217c8bf58dc58ee49214beca710269660dc11a087209adb4；1338 个实体／52 个 DIMENSION／52 个 MTEXT</x:v>
       </x:c>
       <x:c r="K120" s="132" t="str">
-        <x:v>Sail 可采用 monorotaia 单轨滑动系统；官方产品页说明完整滑动门由轨道、门板以及可选门框或侧导向构成</x:v>
+        <x:v>Sail MONOROTAIA 为单轨滑动系统；厂家通用示例标注门板宽 1000 mm、门洞宽 976/989/1978 mm、轨道长 2011/2037/4022 mm、门板高 2670 mm、门洞高 2666/2678 mm</x:v>
       </x:c>
       <x:c r="L120" s="132" t="str">
-        <x:v>产品族与单轨滑动构造</x:v>
+        <x:v>产品族、单轨系统和厂家通用构造尺寸关系</x:v>
       </x:c>
       <x:c r="M120" s="132" t="str">
         <x:v>本项目 M05/M06 最终下单宽高、滑动方向、宿主洞口、轨道固定基层、收口和安装公差</x:v>
@@ -43098,8 +43098,8 @@
       <x:c r="N120" s="132" t="str">
         <x:v>verified_official_family_cad</x:v>
       </x:c>
-      <x:c r="O120" s="132" t="n">
-        <x:v>1</x:v>
+      <x:c r="O120" s="132" t="str">
+        <x:v>1.00</x:v>
       </x:c>
       <x:c r="P120" s="132" t="str">
         <x:v>yes</x:v>
@@ -43116,13 +43116,13 @@
       <x:c r="T120" s="132" t="str">
         <x:v>2023-03</x:v>
       </x:c>
-      <x:c r="U120" s="132"/>
+      <x:c r="U120" s="132" t="str"/>
       <x:c r="V120" s="132" t="str">
         <x:v>none</x:v>
       </x:c>
-      <x:c r="W120" s="132"/>
+      <x:c r="W120" s="132" t="str"/>
       <x:c r="X120" s="132" t="str">
-        <x:v>原始 DWG 已按字节固化；不得仅凭通用 CAD 或文件名关闭项目尺寸与开向</x:v>
+        <x:v>原始 DWG 和 AutoCAD 转换 DXF 已按字节固化；机械审计见 drawings/evidence/RIMADESIO-Sail-monorotaia-mechanical-audit.json；M05 宽 1000 mm 仅与厂家通用示例数值相同，M05 高 2400 mm 与示例 2670 mm 不同，M06 长 1200 mm 与示例轨道 2011/2037/4022 mm 均不同；不得关闭项目尺寸与开向</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -43131,7 +43131,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b444c5d8d634773"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92be6c9264a0498f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/output/forms/滨海湾施工输入清单.xlsx
+++ b/output/forms/滨海湾施工输入清单.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="R12f6e77aaf654ff0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计决策" sheetId="2" r:id="Rb53443d410f34dc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="家电清单" sheetId="3" r:id="R0c1766789ce24516"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设备主表" sheetId="4" r:id="R47205748a0bf472c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安装条件" sheetId="5" r:id="R5f3e027b68514eb4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据索引" sheetId="6" r:id="R9bfd93135eaa4151"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="R4c5883d2fa1a4283"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计决策" sheetId="2" r:id="R0810f7986ab34c9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="家电清单" sheetId="3" r:id="Rc94fa4b790144a05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设备主表" sheetId="4" r:id="R17647ea015f94f4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安装条件" sheetId="5" r:id="R69b02d8dac37430b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据索引" sheetId="6" r:id="R65f0e6b9615d4a6a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2782,9 +2782,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3e106c8b5fe45a2"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc999c6bcdfe14a1c"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra77a463d18d54dc8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0dd89f17ea04ed3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3815,6 +3815,44 @@
         <x:v>实际箱内运行已确认；补底部铭牌与设备功能</x:v>
       </x:c>
     </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>APP-019</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>冰淇淋机</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>甜品设备</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>待确认位置</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>待确认位置</x:v>
+      </x:c>
+      <x:c r="F20" t="str"/>
+      <x:c r="G20" t="str"/>
+      <x:c r="H20" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I20" t="str"/>
+      <x:c r="J20" t="str"/>
+      <x:c r="K20" t="str"/>
+      <x:c r="L20" t="str"/>
+      <x:c r="M20" t="str"/>
+      <x:c r="N20" t="str"/>
+      <x:c r="O20" t="str"/>
+      <x:c r="P20" t="str">
+        <x:v>业主确认新增一台冰淇淋机；未提供品牌、型号、位置或安装资料</x:v>
+      </x:c>
+      <x:c r="Q20" t="str">
+        <x:v>部分确认</x:v>
+      </x:c>
+      <x:c r="R20" t="str">
+        <x:v>候选设备，非已选/已购；不计入 NS-01/NS-02 负荷，待位置和准确型号后再决定插座、回路与给排水。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="Q2:Q19">
     <x:cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="已确认"/>
@@ -3839,7 +3877,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5990f0cd9f2f44c9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7fd00120646e467f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15592,13 +15630,81 @@
         <x:v>APP-017 叠放套装的上部独立设备；产品尺寸不是接口中心。</x:v>
       </x:c>
     </x:row>
+    <x:row r="164">
+      <x:c r="A164" t="str">
+        <x:v>APP-019</x:v>
+      </x:c>
+      <x:c r="B164" t="str">
+        <x:v>APPLIANCE</x:v>
+      </x:c>
+      <x:c r="C164" t="str">
+        <x:v>甜品设备</x:v>
+      </x:c>
+      <x:c r="D164" t="str">
+        <x:v>冰淇淋机</x:v>
+      </x:c>
+      <x:c r="E164" t="str"/>
+      <x:c r="F164" t="str"/>
+      <x:c r="G164" t="str"/>
+      <x:c r="H164" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I164" t="str">
+        <x:v>candidate</x:v>
+      </x:c>
+      <x:c r="J164" t="str">
+        <x:v>partial</x:v>
+      </x:c>
+      <x:c r="K164" t="str">
+        <x:v>待确认位置</x:v>
+      </x:c>
+      <x:c r="L164" t="str">
+        <x:v>待确认位置</x:v>
+      </x:c>
+      <x:c r="M164" t="str"/>
+      <x:c r="N164" t="str"/>
+      <x:c r="O164" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="P164" t="str">
+        <x:v>logical_input</x:v>
+      </x:c>
+      <x:c r="Q164" t="str">
+        <x:v>APP-019</x:v>
+      </x:c>
+      <x:c r="R164" t="str"/>
+      <x:c r="S164" t="str"/>
+      <x:c r="T164" t="str"/>
+      <x:c r="U164" t="str"/>
+      <x:c r="V164" t="str">
+        <x:v>OWNER-INPUT-APP019-20260815</x:v>
+      </x:c>
+      <x:c r="W164" t="str">
+        <x:v>业主确认新增一台冰淇淋机；未提供品牌、型号、位置或安装资料</x:v>
+      </x:c>
+      <x:c r="X164" t="str">
+        <x:v>1.00</x:v>
+      </x:c>
+      <x:c r="Y164" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="Z164" t="str">
+        <x:v>appliance</x:v>
+      </x:c>
+      <x:c r="AA164" t="str">
+        <x:v>APP-019</x:v>
+      </x:c>
+      <x:c r="AB164" t="str">
+        <x:v>候选设备，非已选/已购；不计入 NS-01/NS-02 负荷，待位置和准确型号后再决定插座、回路与给排水。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:AB1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c8ac1a5c68c405c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbfc7efc78db4e2b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44986,132 +45092,616 @@
       </x:c>
     </x:row>
     <x:row r="821" ht="31.5" customHeight="1">
-      <x:c r="A821" s="189"/>
-      <x:c r="B821" s="189"/>
-      <x:c r="C821" s="189"/>
-      <x:c r="D821" s="189"/>
-      <x:c r="E821" s="189"/>
-      <x:c r="F821" s="189"/>
-      <x:c r="G821" s="189"/>
-      <x:c r="H821" s="189"/>
-      <x:c r="I821" s="189"/>
-      <x:c r="J821" s="189"/>
-      <x:c r="K821" s="189"/>
-      <x:c r="L821" s="189"/>
-      <x:c r="M821" s="189"/>
-      <x:c r="N821" s="189"/>
+      <x:c r="A821" s="189" t="str">
+        <x:v>REQ-APP019-001</x:v>
+      </x:c>
+      <x:c r="B821" s="189" t="str">
+        <x:v>APP-019</x:v>
+      </x:c>
+      <x:c r="C821" s="189" t="str">
+        <x:v>ELEC</x:v>
+      </x:c>
+      <x:c r="D821" s="189" t="str">
+        <x:v>rated_power</x:v>
+      </x:c>
+      <x:c r="E821" s="189" t="str"/>
+      <x:c r="F821" s="189" t="str"/>
+      <x:c r="G821" s="189" t="str">
+        <x:v>W</x:v>
+      </x:c>
+      <x:c r="H821" s="189" t="str"/>
+      <x:c r="I821" s="189" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="J821" s="189" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="K821" s="189" t="str">
+        <x:v>OWNER-INPUT-APP019-20260815</x:v>
+      </x:c>
+      <x:c r="L821" s="189" t="str">
+        <x:v>业主仅确认设备类别与数量</x:v>
+      </x:c>
+      <x:c r="M821" s="189" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="N821" s="189" t="str">
+        <x:v>保持 unknown；关闭证据：准确型号名牌功率。</x:v>
+      </x:c>
     </x:row>
     <x:row r="822" ht="31.5" customHeight="1">
-      <x:c r="A822" s="189"/>
-      <x:c r="B822" s="189"/>
-      <x:c r="C822" s="189"/>
-      <x:c r="D822" s="189"/>
-      <x:c r="E822" s="189"/>
-      <x:c r="F822" s="189"/>
-      <x:c r="G822" s="189"/>
-      <x:c r="H822" s="189"/>
-      <x:c r="I822" s="189"/>
-      <x:c r="J822" s="189"/>
-      <x:c r="K822" s="189"/>
-      <x:c r="L822" s="189"/>
-      <x:c r="M822" s="189"/>
-      <x:c r="N822" s="189"/>
+      <x:c r="A822" s="189" t="str">
+        <x:v>REQ-APP019-002</x:v>
+      </x:c>
+      <x:c r="B822" s="189" t="str">
+        <x:v>APP-019</x:v>
+      </x:c>
+      <x:c r="C822" s="189" t="str">
+        <x:v>ELEC</x:v>
+      </x:c>
+      <x:c r="D822" s="189" t="str">
+        <x:v>simultaneous_group</x:v>
+      </x:c>
+      <x:c r="E822" s="189" t="str"/>
+      <x:c r="F822" s="189" t="str"/>
+      <x:c r="G822" s="189" t="str"/>
+      <x:c r="H822" s="189" t="str"/>
+      <x:c r="I822" s="189" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="J822" s="189" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="K822" s="189" t="str">
+        <x:v>OWNER-INPUT-APP019-20260815</x:v>
+      </x:c>
+      <x:c r="L822" s="189" t="str">
+        <x:v>业主仅确认设备类别与数量</x:v>
+      </x:c>
+      <x:c r="M822" s="189" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="N822" s="189" t="str">
+        <x:v>保持 unknown；关闭证据：使用位置和同时工况。</x:v>
+      </x:c>
     </x:row>
     <x:row r="823" ht="31.5" customHeight="1">
-      <x:c r="A823" s="189"/>
-      <x:c r="B823" s="189"/>
-      <x:c r="C823" s="189"/>
-      <x:c r="D823" s="189"/>
-      <x:c r="E823" s="189"/>
-      <x:c r="F823" s="189"/>
-      <x:c r="G823" s="189"/>
-      <x:c r="H823" s="189"/>
-      <x:c r="I823" s="189"/>
-      <x:c r="J823" s="189"/>
-      <x:c r="K823" s="189"/>
-      <x:c r="L823" s="189"/>
-      <x:c r="M823" s="189"/>
-      <x:c r="N823" s="189"/>
+      <x:c r="A823" s="189" t="str">
+        <x:v>REQ-APP019-003</x:v>
+      </x:c>
+      <x:c r="B823" s="189" t="str">
+        <x:v>APP-019</x:v>
+      </x:c>
+      <x:c r="C823" s="189" t="str">
+        <x:v>PLUM</x:v>
+      </x:c>
+      <x:c r="D823" s="189" t="str">
+        <x:v>water_required</x:v>
+      </x:c>
+      <x:c r="E823" s="189" t="str"/>
+      <x:c r="F823" s="189" t="str"/>
+      <x:c r="G823" s="189" t="str"/>
+      <x:c r="H823" s="189" t="str"/>
+      <x:c r="I823" s="189" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="J823" s="189" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="K823" s="189" t="str">
+        <x:v>OWNER-INPUT-APP019-20260815</x:v>
+      </x:c>
+      <x:c r="L823" s="189" t="str">
+        <x:v>业主仅确认设备类别与数量</x:v>
+      </x:c>
+      <x:c r="M823" s="189" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="N823" s="189" t="str">
+        <x:v>保持 unknown；关闭证据：准确型号安装图。</x:v>
+      </x:c>
     </x:row>
     <x:row r="824" ht="31.5" customHeight="1">
-      <x:c r="A824" s="189"/>
-      <x:c r="B824" s="189"/>
-      <x:c r="C824" s="189"/>
-      <x:c r="D824" s="189"/>
-      <x:c r="E824" s="189"/>
-      <x:c r="F824" s="189"/>
-      <x:c r="G824" s="189"/>
-      <x:c r="H824" s="189"/>
-      <x:c r="I824" s="189"/>
-      <x:c r="J824" s="189"/>
-      <x:c r="K824" s="189"/>
-      <x:c r="L824" s="189"/>
-      <x:c r="M824" s="189"/>
-      <x:c r="N824" s="189"/>
+      <x:c r="A824" s="189" t="str">
+        <x:v>REQ-APP019-004</x:v>
+      </x:c>
+      <x:c r="B824" s="189" t="str">
+        <x:v>APP-019</x:v>
+      </x:c>
+      <x:c r="C824" s="189" t="str">
+        <x:v>PLUM</x:v>
+      </x:c>
+      <x:c r="D824" s="189" t="str">
+        <x:v>drain_required</x:v>
+      </x:c>
+      <x:c r="E824" s="189" t="str"/>
+      <x:c r="F824" s="189" t="str"/>
+      <x:c r="G824" s="189" t="str"/>
+      <x:c r="H824" s="189" t="str"/>
+      <x:c r="I824" s="189" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="J824" s="189" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="K824" s="189" t="str">
+        <x:v>OWNER-INPUT-APP019-20260815</x:v>
+      </x:c>
+      <x:c r="L824" s="189" t="str">
+        <x:v>业主仅确认设备类别与数量</x:v>
+      </x:c>
+      <x:c r="M824" s="189" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="N824" s="189" t="str">
+        <x:v>保持 unknown；关闭证据：准确型号安装图。</x:v>
+      </x:c>
     </x:row>
     <x:row r="825" ht="31.5" customHeight="1">
-      <x:c r="A825" s="189"/>
-      <x:c r="B825" s="189"/>
-      <x:c r="C825" s="189"/>
-      <x:c r="D825" s="189"/>
-      <x:c r="E825" s="189"/>
-      <x:c r="F825" s="189"/>
-      <x:c r="G825" s="189"/>
-      <x:c r="H825" s="189"/>
-      <x:c r="I825" s="189"/>
-      <x:c r="J825" s="189"/>
-      <x:c r="K825" s="189"/>
-      <x:c r="L825" s="189"/>
-      <x:c r="M825" s="189"/>
-      <x:c r="N825" s="189"/>
+      <x:c r="A825" s="189" t="str">
+        <x:v>REQ-APP019-005</x:v>
+      </x:c>
+      <x:c r="B825" s="189" t="str">
+        <x:v>APP-019</x:v>
+      </x:c>
+      <x:c r="C825" s="189" t="str">
+        <x:v>GAS</x:v>
+      </x:c>
+      <x:c r="D825" s="189" t="str">
+        <x:v>gas_required</x:v>
+      </x:c>
+      <x:c r="E825" s="189" t="str"/>
+      <x:c r="F825" s="189" t="str"/>
+      <x:c r="G825" s="189" t="str"/>
+      <x:c r="H825" s="189" t="str"/>
+      <x:c r="I825" s="189" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="J825" s="189" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="K825" s="189" t="str">
+        <x:v>OWNER-INPUT-APP019-20260815</x:v>
+      </x:c>
+      <x:c r="L825" s="189" t="str">
+        <x:v>业主仅确认设备类别与数量</x:v>
+      </x:c>
+      <x:c r="M825" s="189" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="N825" s="189" t="str">
+        <x:v>保持 unknown；关闭证据：准确型号安装图。</x:v>
+      </x:c>
     </x:row>
     <x:row r="826" ht="31.5" customHeight="1">
-      <x:c r="A826" s="189"/>
-      <x:c r="B826" s="189"/>
-      <x:c r="C826" s="189"/>
-      <x:c r="D826" s="189"/>
-      <x:c r="E826" s="189"/>
-      <x:c r="F826" s="189"/>
-      <x:c r="G826" s="189"/>
-      <x:c r="H826" s="189"/>
-      <x:c r="I826" s="189"/>
-      <x:c r="J826" s="189"/>
-      <x:c r="K826" s="189"/>
-      <x:c r="L826" s="189"/>
-      <x:c r="M826" s="189"/>
-      <x:c r="N826" s="189"/>
+      <x:c r="A826" s="189" t="str">
+        <x:v>REQ-APP019-006</x:v>
+      </x:c>
+      <x:c r="B826" s="189" t="str">
+        <x:v>APP-019</x:v>
+      </x:c>
+      <x:c r="C826" s="189" t="str">
+        <x:v>HVAC/INT1</x:v>
+      </x:c>
+      <x:c r="D826" s="189" t="str">
+        <x:v>ventilation_required</x:v>
+      </x:c>
+      <x:c r="E826" s="189" t="str"/>
+      <x:c r="F826" s="189" t="str"/>
+      <x:c r="G826" s="189" t="str"/>
+      <x:c r="H826" s="189" t="str"/>
+      <x:c r="I826" s="189" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="J826" s="189" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="K826" s="189" t="str">
+        <x:v>OWNER-INPUT-APP019-20260815</x:v>
+      </x:c>
+      <x:c r="L826" s="189" t="str">
+        <x:v>业主仅确认设备类别与数量</x:v>
+      </x:c>
+      <x:c r="M826" s="189" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="N826" s="189" t="str">
+        <x:v>保持 unknown；关闭证据：准确型号散热和净距要求。</x:v>
+      </x:c>
     </x:row>
     <x:row r="827" ht="31.5" customHeight="1">
-      <x:c r="A827" s="189"/>
-      <x:c r="B827" s="189"/>
-      <x:c r="C827" s="189"/>
-      <x:c r="D827" s="189"/>
-      <x:c r="E827" s="189"/>
-      <x:c r="F827" s="189"/>
-      <x:c r="G827" s="189"/>
-      <x:c r="H827" s="189"/>
-      <x:c r="I827" s="189"/>
-      <x:c r="J827" s="189"/>
-      <x:c r="K827" s="189"/>
-      <x:c r="L827" s="189"/>
-      <x:c r="M827" s="189"/>
-      <x:c r="N827" s="189"/>
+      <x:c r="A827" s="189" t="str">
+        <x:v>REQ-APP019-007</x:v>
+      </x:c>
+      <x:c r="B827" s="189" t="str">
+        <x:v>APP-019</x:v>
+      </x:c>
+      <x:c r="C827" s="189" t="str">
+        <x:v>INT1</x:v>
+      </x:c>
+      <x:c r="D827" s="189" t="str">
+        <x:v>installation_mode</x:v>
+      </x:c>
+      <x:c r="E827" s="189" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="F827" s="189" t="str"/>
+      <x:c r="G827" s="189" t="str"/>
+      <x:c r="H827" s="189" t="str"/>
+      <x:c r="I827" s="189" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="J827" s="189" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="K827" s="189" t="str">
+        <x:v>OWNER-INPUT-APP019-20260815</x:v>
+      </x:c>
+      <x:c r="L827" s="189" t="str">
+        <x:v>业主仅确认设备类别与数量</x:v>
+      </x:c>
+      <x:c r="M827" s="189" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="N827" s="189" t="str">
+        <x:v>保持 unknown；关闭证据：台面、落地或嵌入形式。</x:v>
+      </x:c>
     </x:row>
     <x:row r="828" ht="31.5" customHeight="1">
-      <x:c r="A828" s="189"/>
-      <x:c r="B828" s="189"/>
-      <x:c r="C828" s="189"/>
-      <x:c r="D828" s="189"/>
-      <x:c r="E828" s="189"/>
-      <x:c r="F828" s="189"/>
-      <x:c r="G828" s="189"/>
-      <x:c r="H828" s="189"/>
-      <x:c r="I828" s="189"/>
-      <x:c r="J828" s="189"/>
-      <x:c r="K828" s="189"/>
-      <x:c r="L828" s="189"/>
-      <x:c r="M828" s="189"/>
-      <x:c r="N828" s="189"/>
+      <x:c r="A828" s="189" t="str">
+        <x:v>REQ-APP019-008</x:v>
+      </x:c>
+      <x:c r="B828" s="189" t="str">
+        <x:v>APP-019</x:v>
+      </x:c>
+      <x:c r="C828" s="189" t="str">
+        <x:v>ELEC</x:v>
+      </x:c>
+      <x:c r="D828" s="189" t="str">
+        <x:v>appliance_plug_rating_a</x:v>
+      </x:c>
+      <x:c r="E828" s="189" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="F828" s="189" t="str"/>
+      <x:c r="G828" s="189" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H828" s="189" t="str"/>
+      <x:c r="I828" s="189" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="J828" s="189" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="K828" s="189" t="str">
+        <x:v>OWNER-INPUT-APP019-20260815</x:v>
+      </x:c>
+      <x:c r="L828" s="189" t="str">
+        <x:v>业主仅确认设备类别与数量</x:v>
+      </x:c>
+      <x:c r="M828" s="189" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="N828" s="189" t="str">
+        <x:v>保持 unknown；关闭证据：实物插头或厂家电气页。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="829">
+      <x:c r="A829" t="str">
+        <x:v>REQ-APP019-009</x:v>
+      </x:c>
+      <x:c r="B829" t="str">
+        <x:v>APP-019</x:v>
+      </x:c>
+      <x:c r="C829" t="str">
+        <x:v>ELEC</x:v>
+      </x:c>
+      <x:c r="D829" t="str">
+        <x:v>wall_socket_rating_a</x:v>
+      </x:c>
+      <x:c r="E829" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="F829" t="str"/>
+      <x:c r="G829" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H829" t="str"/>
+      <x:c r="I829" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="J829" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="K829" t="str">
+        <x:v>OWNER-INPUT-APP019-20260815</x:v>
+      </x:c>
+      <x:c r="L829" t="str">
+        <x:v>业主仅确认设备类别与数量</x:v>
+      </x:c>
+      <x:c r="M829" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="N829" t="str">
+        <x:v>保持 unknown；关闭证据：按实购插头和支路计算匹配。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="830">
+      <x:c r="A830" t="str">
+        <x:v>REQ-APP019-010</x:v>
+      </x:c>
+      <x:c r="B830" t="str">
+        <x:v>APP-019</x:v>
+      </x:c>
+      <x:c r="C830" t="str">
+        <x:v>ELEC</x:v>
+      </x:c>
+      <x:c r="D830" t="str">
+        <x:v>branch_breaker_rating_a</x:v>
+      </x:c>
+      <x:c r="E830" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="F830" t="str"/>
+      <x:c r="G830" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="H830" t="str"/>
+      <x:c r="I830" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="J830" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="K830" t="str">
+        <x:v>OWNER-INPUT-APP019-20260815</x:v>
+      </x:c>
+      <x:c r="L830" t="str">
+        <x:v>业主仅确认设备类别与数量</x:v>
+      </x:c>
+      <x:c r="M830" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="N830" t="str">
+        <x:v>保持 unknown；关闭证据：名牌负荷、同时工况和回路计算。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="831">
+      <x:c r="A831" t="str">
+        <x:v>REQ-APP019-011</x:v>
+      </x:c>
+      <x:c r="B831" t="str">
+        <x:v>APP-019</x:v>
+      </x:c>
+      <x:c r="C831" t="str">
+        <x:v>ELEC</x:v>
+      </x:c>
+      <x:c r="D831" t="str">
+        <x:v>dedicated_branch_circuit</x:v>
+      </x:c>
+      <x:c r="E831" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="F831" t="str"/>
+      <x:c r="G831" t="str"/>
+      <x:c r="H831" t="str"/>
+      <x:c r="I831" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="J831" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="K831" t="str">
+        <x:v>OWNER-INPUT-APP019-20260815</x:v>
+      </x:c>
+      <x:c r="L831" t="str">
+        <x:v>业主仅确认设备类别与数量</x:v>
+      </x:c>
+      <x:c r="M831" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="N831" t="str">
+        <x:v>保持 unknown；关闭证据：名牌负荷、位置和共路工况。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="832">
+      <x:c r="A832" t="str">
+        <x:v>REQ-APP019-012</x:v>
+      </x:c>
+      <x:c r="B832" t="str">
+        <x:v>APP-019</x:v>
+      </x:c>
+      <x:c r="C832" t="str">
+        <x:v>INT1</x:v>
+      </x:c>
+      <x:c r="D832" t="str">
+        <x:v>product_width</x:v>
+      </x:c>
+      <x:c r="E832" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="F832" t="str"/>
+      <x:c r="G832" t="str">
+        <x:v>mm</x:v>
+      </x:c>
+      <x:c r="H832" t="str"/>
+      <x:c r="I832" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="J832" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="K832" t="str">
+        <x:v>OWNER-INPUT-APP019-20260815</x:v>
+      </x:c>
+      <x:c r="L832" t="str">
+        <x:v>业主仅确认设备类别与数量</x:v>
+      </x:c>
+      <x:c r="M832" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="N832" t="str">
+        <x:v>保持 unknown；关闭证据：准确型号尺寸图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="833">
+      <x:c r="A833" t="str">
+        <x:v>REQ-APP019-013</x:v>
+      </x:c>
+      <x:c r="B833" t="str">
+        <x:v>APP-019</x:v>
+      </x:c>
+      <x:c r="C833" t="str">
+        <x:v>INT1</x:v>
+      </x:c>
+      <x:c r="D833" t="str">
+        <x:v>product_height</x:v>
+      </x:c>
+      <x:c r="E833" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="F833" t="str"/>
+      <x:c r="G833" t="str">
+        <x:v>mm</x:v>
+      </x:c>
+      <x:c r="H833" t="str"/>
+      <x:c r="I833" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="J833" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="K833" t="str">
+        <x:v>OWNER-INPUT-APP019-20260815</x:v>
+      </x:c>
+      <x:c r="L833" t="str">
+        <x:v>业主仅确认设备类别与数量</x:v>
+      </x:c>
+      <x:c r="M833" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="N833" t="str">
+        <x:v>保持 unknown；关闭证据：准确型号尺寸图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="834">
+      <x:c r="A834" t="str">
+        <x:v>REQ-APP019-014</x:v>
+      </x:c>
+      <x:c r="B834" t="str">
+        <x:v>APP-019</x:v>
+      </x:c>
+      <x:c r="C834" t="str">
+        <x:v>INT1</x:v>
+      </x:c>
+      <x:c r="D834" t="str">
+        <x:v>product_depth</x:v>
+      </x:c>
+      <x:c r="E834" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="F834" t="str"/>
+      <x:c r="G834" t="str">
+        <x:v>mm</x:v>
+      </x:c>
+      <x:c r="H834" t="str"/>
+      <x:c r="I834" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="J834" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="K834" t="str">
+        <x:v>OWNER-INPUT-APP019-20260815</x:v>
+      </x:c>
+      <x:c r="L834" t="str">
+        <x:v>业主仅确认设备类别与数量</x:v>
+      </x:c>
+      <x:c r="M834" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="N834" t="str">
+        <x:v>保持 unknown；关闭证据：准确型号尺寸图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="835">
+      <x:c r="A835" t="str">
+        <x:v>REQ-APP019-015</x:v>
+      </x:c>
+      <x:c r="B835" t="str">
+        <x:v>APP-019</x:v>
+      </x:c>
+      <x:c r="C835" t="str">
+        <x:v>INT1</x:v>
+      </x:c>
+      <x:c r="D835" t="str">
+        <x:v>service_clearance</x:v>
+      </x:c>
+      <x:c r="E835" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="F835" t="str"/>
+      <x:c r="G835" t="str">
+        <x:v>mm</x:v>
+      </x:c>
+      <x:c r="H835" t="str"/>
+      <x:c r="I835" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="J835" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="K835" t="str">
+        <x:v>OWNER-INPUT-APP019-20260815</x:v>
+      </x:c>
+      <x:c r="L835" t="str">
+        <x:v>业主仅确认设备类别与数量</x:v>
+      </x:c>
+      <x:c r="M835" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="N835" t="str">
+        <x:v>保持 unknown；关闭证据：厂家散热、操作和检修要求。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="836">
+      <x:c r="A836" t="str">
+        <x:v>REQ-APP019-016</x:v>
+      </x:c>
+      <x:c r="B836" t="str">
+        <x:v>APP-019</x:v>
+      </x:c>
+      <x:c r="C836" t="str">
+        <x:v>MULTI</x:v>
+      </x:c>
+      <x:c r="D836" t="str">
+        <x:v>interface_center_coordinates</x:v>
+      </x:c>
+      <x:c r="E836" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="F836" t="str"/>
+      <x:c r="G836" t="str"/>
+      <x:c r="H836" t="str"/>
+      <x:c r="I836" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="J836" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="K836" t="str">
+        <x:v>OWNER-INPUT-APP019-20260815</x:v>
+      </x:c>
+      <x:c r="L836" t="str">
+        <x:v>业主仅确认设备类别与数量</x:v>
+      </x:c>
+      <x:c r="M836" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="N836" t="str">
+        <x:v>保持 unknown；关闭证据：厂家安装图与项目定位。</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -45119,7 +45709,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ab72e9b49f74bfa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3762d03ab23049c3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -57020,13 +57610,77 @@
         <x:v>请求包只定义最短关闭证据，不把待回复字段标为已确认。</x:v>
       </x:c>
     </x:row>
+    <x:row r="183">
+      <x:c r="A183" t="str">
+        <x:v>OWNER-INPUT-APP019-20260815</x:v>
+      </x:c>
+      <x:c r="B183" t="str">
+        <x:v>ELEC/PLUM/INT1</x:v>
+      </x:c>
+      <x:c r="C183" t="str">
+        <x:v>E-303/P-201/P-202/INT1/S-701</x:v>
+      </x:c>
+      <x:c r="D183" t="str">
+        <x:v>APP-019 冰淇淋机设备类别与数量</x:v>
+      </x:c>
+      <x:c r="E183" t="str">
+        <x:v>owner_confirmation</x:v>
+      </x:c>
+      <x:c r="F183" t="str">
+        <x:v>drawings/evidence/OWNER-INPUT-APP-019-20260815.md</x:v>
+      </x:c>
+      <x:c r="G183" t="str"/>
+      <x:c r="H183" t="str">
+        <x:v>drawings/evidence/OWNER-INPUT-APP-019-20260815.md</x:v>
+      </x:c>
+      <x:c r="I183" t="str">
+        <x:v>0004eeccf0a7f076485a2bf5d663df6e7ab26cf696398639728d8fbb5e4d614c</x:v>
+      </x:c>
+      <x:c r="J183" t="str">
+        <x:v>业主新增一台冰淇淋机</x:v>
+      </x:c>
+      <x:c r="K183" t="str">
+        <x:v>业主确认新增冰淇淋机 1 台</x:v>
+      </x:c>
+      <x:c r="L183" t="str">
+        <x:v>项目需要登记一台冰淇淋机</x:v>
+      </x:c>
+      <x:c r="M183" t="str">
+        <x:v>已采购、品牌型号、位置、安装形式、功率、插头插座、回路、给排水、尺寸或接口中心</x:v>
+      </x:c>
+      <x:c r="N183" t="str">
+        <x:v>confirmed_owner_input_identity_only</x:v>
+      </x:c>
+      <x:c r="O183" t="str">
+        <x:v>1.00</x:v>
+      </x:c>
+      <x:c r="P183" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="Q183" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="R183" t="str"/>
+      <x:c r="S183" t="str"/>
+      <x:c r="T183" t="str">
+        <x:v>2026-08-15</x:v>
+      </x:c>
+      <x:c r="U183" t="str">
+        <x:v>2026-08-15</x:v>
+      </x:c>
+      <x:c r="V183" t="str"/>
+      <x:c r="W183" t="str"/>
+      <x:c r="X183" t="str">
+        <x:v>只登记设备类别与数量；所有安装参数保持 unknown。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:X1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66fbc29859dd45a1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34695669162a424f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/output/forms/滨海湾施工输入清单.xlsx
+++ b/output/forms/滨海湾施工输入清单.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="Rbd46ed411e4a4a36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计决策" sheetId="2" r:id="R5d54f68acb304563"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="家电清单" sheetId="3" r:id="R4412bc6ac1374aad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设备主表" sheetId="4" r:id="R8802052495634f1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安装条件" sheetId="5" r:id="R32c8e33e8a6c42e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据索引" sheetId="6" r:id="Rd493968cc0ef4e0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="Rc6ec1f5047484ce2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计决策" sheetId="2" r:id="Rf8bef2e4490f46ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="家电清单" sheetId="3" r:id="R5e9b4b7b3e6f4715"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设备主表" sheetId="4" r:id="Rfbba4d7f8ffc46ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安装条件" sheetId="5" r:id="R12b65a8c01584d74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据索引" sheetId="6" r:id="R82ec7029561140fb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2612,14 +2612,14 @@
         <x:v>按最终产品逐台收集安装图；存放位置不得代替使用和接口位置</x:v>
       </x:c>
       <x:c r="G23" s="232" t="str">
-        <x:v>MS 已确认洗烘、VVD、定制地漏和石材盆方向；Foster 官方尺寸已内部核验；剩余项目加工接口见 09 表及 2026-08-18 最短清单</x:v>
+        <x:v>MS 已确认洗烘、VVD、定制地漏和石材盆方向；Foster 官方尺寸已内部核验；剩余厨房项目加工接口见 09 表</x:v>
       </x:c>
       <x:c r="H23" s="189"/>
       <x:c r="I23" s="232" t="str">
         <x:v>需证据</x:v>
       </x:c>
       <x:c r="J23" s="232" t="str">
-        <x:v>OUTBOUND-FORM-PLUM-20260817;OWNER-RESPONSE-HVAC-PLUM-20260818;EXT-MINIMAL-LIST-20260818</x:v>
+        <x:v>OUTBOUND-FORM-PLUM-20260817;OWNER-RESPONSE-HVAC-PLUM-20260818;OUTBOUND-FORM-KITCHEN-20260818</x:v>
       </x:c>
       <x:c r="K23" s="189" t="str">
         <x:v>现有模型端点不是正式 IfcDistributionPort</x:v>
@@ -3740,9 +3740,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4af39c534bce4920"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0d4c6ae6c4a4208"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f3ab65f85f04deb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf5233c065174122"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4835,7 +4835,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2cd8aae72bc749b4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41e2ccadd84c4f16"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16954,7 +16954,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01d739c6a1c2497d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdadca3508b2545d8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49675,7 +49675,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3da96c4336f9485e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87d92e5042a849fb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -62047,7 +62047,7 @@
         <x:v>A-001/PM/QA01</x:v>
       </x:c>
       <x:c r="D190" s="189" t="str">
-        <x:v>当前外部信息最短清单与分发入口</x:v>
+        <x:v>2026-08-17 外部信息清单历史快照</x:v>
       </x:c>
       <x:c r="E190" s="189" t="str">
         <x:v>project_external_evidence_request_package</x:v>
@@ -62055,24 +62055,24 @@
       <x:c r="F190" s="189" t="str">
         <x:v>drawings/evidence/EXT-外部信息最短清单-20260817.md</x:v>
       </x:c>
-      <x:c r="G190" s="189"/>
+      <x:c r="G190" s="189" t="str"/>
       <x:c r="H190" s="189" t="str">
         <x:v>drawings/evidence/EXT-外部信息最短清单-20260817.md</x:v>
       </x:c>
       <x:c r="I190" s="189" t="str">
-        <x:v>fbfef96c1491e8c61e1fc38623299bc35f10a9a01a1f833e4b912c9de9141246</x:v>
+        <x:v>e54586cb286b9f55b282315aee5287b5a108e059fc4314a08c319eab0522da92</x:v>
       </x:c>
       <x:c r="J190" s="189" t="str">
-        <x:v>先发出的 4 份现成文件；厂家／现场／主管部门／业主偏好；当前结论</x:v>
+        <x:v>当时先发出的 4 份文件；厂家／现场／主管部门／业主偏好；当时结论</x:v>
       </x:c>
       <x:c r="K190" s="189" t="str">
-        <x:v>把 33 项无保留发布阻断和 19 个稳定证据包压缩为可直接分发的四类最短清单，并链接 4 份现成关闭包</x:v>
+        <x:v>保留 2026-08-17 当日外部证据边界和分发记录</x:v>
       </x:c>
       <x:c r="L190" s="189" t="str">
-        <x:v>当前缺失证据、责任方、受影响图纸和可执行分发入口已完整整理</x:v>
+        <x:v>仅证明 2026-08-17 的历史状态</x:v>
       </x:c>
       <x:c r="M190" s="189" t="str">
-        <x:v>2026-08-18 当前外部清单；现行版本见 EXT-MINIMAL-LIST-20260818</x:v>
+        <x:v>当前派件内容、外部方已回复或任何项目接口已冻结</x:v>
       </x:c>
       <x:c r="N190" s="189" t="str">
         <x:v>superseded_project_external_closeout_index</x:v>
@@ -62086,16 +62086,16 @@
       <x:c r="Q190" s="189" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="R190" s="189"/>
-      <x:c r="S190" s="189"/>
+      <x:c r="R190" s="189" t="str"/>
+      <x:c r="S190" s="189" t="str"/>
       <x:c r="T190" s="189" t="str">
         <x:v>2026-08-17</x:v>
       </x:c>
       <x:c r="U190" s="189" t="str">
         <x:v>2026-08-17</x:v>
       </x:c>
-      <x:c r="V190" s="189"/>
-      <x:c r="W190" s="189"/>
+      <x:c r="V190" s="189" t="str"/>
+      <x:c r="W190" s="189" t="str"/>
       <x:c r="X190" s="189" t="str">
         <x:v>保留为 2026-08-17 历史状态；不得继续作为现行发件清单。</x:v>
       </x:c>
@@ -63742,44 +63742,44 @@
     </x:row>
     <x:row r="216" ht="31.5" customHeight="1">
       <x:c r="A216" s="189" t="str">
-        <x:v>EXT-MINIMAL-LIST-20260818</x:v>
+        <x:v>OWNER-INT1-WINDOW-TREATMENTS-20260818</x:v>
       </x:c>
       <x:c r="B216" s="189" t="str">
-        <x:v>PM/QA01</x:v>
+        <x:v>INT1/WFIN/ELEC</x:v>
       </x:c>
       <x:c r="C216" s="189" t="str">
-        <x:v>A-001/GANTT</x:v>
+        <x:v>A-104/A-106/E-303/S-701</x:v>
       </x:c>
       <x:c r="D216" s="189" t="str">
-        <x:v>2026-08-18 当前外部证据最短清单</x:v>
+        <x:v>全屋窗饰设计方向与卧室夜帘候选</x:v>
       </x:c>
       <x:c r="E216" s="189" t="str">
-        <x:v>project_external_closeout_index</x:v>
+        <x:v>owner_confirmation_with_official_product_research</x:v>
       </x:c>
       <x:c r="F216" s="189" t="str">
-        <x:v>EXT-外部信息最短清单-20260818.md</x:v>
-      </x:c>
-      <x:c r="G216" s="189"/>
+        <x:v>OWNER-INT1-全屋窗饰方案-20260818.md</x:v>
+      </x:c>
+      <x:c r="G216" s="189" t="str"/>
       <x:c r="H216" s="189" t="str">
-        <x:v>drawings/evidence/EXT-外部信息最短清单-20260818.md</x:v>
+        <x:v>drawings/evidence/OWNER-INT1-全屋窗饰方案-20260818.md</x:v>
       </x:c>
       <x:c r="I216" s="189" t="str">
-        <x:v>bea1603a86401fb192e588d51595d230ccd1b9e58a14d17ae0ffb864d07f9bf5</x:v>
+        <x:v>319afadd3ec1308eadee50d7422f977621b05d540411620de8c26a25df07f49a</x:v>
       </x:c>
       <x:c r="J216" s="189" t="str">
-        <x:v>直接发出的文件；西门子洗烘；定制地漏；已关闭；业主偏好</x:v>
+        <x:v>2026-08-18 业主口径；亨特道格拉斯官方产品链接；A-104 名义窗组</x:v>
       </x:c>
       <x:c r="K216" s="189" t="str">
-        <x:v>把 MS 已回复项从对外询问中移除，并按收件人列出最短回复内容</x:v>
+        <x:v>萝美雅／丝络雅／25 mm 铝百叶方向已确认；卧室夜帘收敛为 LightLock 全黑优先与 Silhouette Duolite 报价安装优先两案</x:v>
       </x:c>
       <x:c r="L216" s="189" t="str">
-        <x:v>当前外部关闭路径与内部已关闭边界</x:v>
+        <x:v>当前窗饰产品家族与颜色方向及夜帘候选和排除边界</x:v>
       </x:c>
       <x:c r="M216" s="189" t="str">
-        <x:v>任何外部证据已返回</x:v>
+        <x:v>夜帘已终选或下单；实体色卡已批准；完成面尺寸／分幅／头轨／侧轨／电源／控制／安装图已冻结</x:v>
       </x:c>
       <x:c r="N216" s="189" t="str">
-        <x:v>verified_current_external_closeout_index</x:v>
+        <x:v>confirmed_day_shades_night_shortlist_quote_install_pending</x:v>
       </x:c>
       <x:c r="O216" s="189" t="str">
         <x:v>1.00</x:v>
@@ -63790,17 +63790,23 @@
       <x:c r="Q216" s="189" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="R216" s="189"/>
-      <x:c r="S216" s="189"/>
+      <x:c r="R216" s="189" t="str">
+        <x:v>Hunter Douglas</x:v>
+      </x:c>
+      <x:c r="S216" s="189" t="str">
+        <x:v>Luminette;Silhouette;25 mm Venetian;Duette LightLock;Silhouette Duolite</x:v>
+      </x:c>
       <x:c r="T216" s="189" t="str">
         <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="U216" s="189" t="str">
         <x:v>2026-08-18</x:v>
       </x:c>
-      <x:c r="V216" s="189"/>
-      <x:c r="W216" s="189"/>
-      <x:c r="X216" s="189"/>
+      <x:c r="V216" s="189" t="str"/>
+      <x:c r="W216" s="189" t="str"/>
+      <x:c r="X216" s="189" t="str">
+        <x:v>只记录设计方向和候选边界；不新增正式 IFC 窗饰对象或推导下单尺寸。</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -63808,7 +63814,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc88e6f1afdf844f5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc30fc841b1342c3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/output/forms/滨海湾施工输入清单.xlsx
+++ b/output/forms/滨海湾施工输入清单.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="R9c94d98317644cdd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计决策" sheetId="2" r:id="R7e2ab5a404f94f6b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="家电清单" sheetId="3" r:id="R20454ac0537a44e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设备主表" sheetId="4" r:id="R408427596d054afd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安装条件" sheetId="5" r:id="R3b8be1e8f7704742"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据索引" sheetId="6" r:id="R831abf1af55048a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="R58d1b5936a6a4a9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计决策" sheetId="2" r:id="Rd10369d037a3468a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="家电清单" sheetId="3" r:id="R888c17b09c324f38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设备主表" sheetId="4" r:id="R1f8fd684d06442cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安装条件" sheetId="5" r:id="Ra55932c8c74b4b25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据索引" sheetId="6" r:id="R5fa247efc1b647be"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3781,9 +3781,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5487233638ae46b2"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4974ba33bbd846f2"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2036a57258cc4711"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb84266a213f4070"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4876,7 +4876,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra21a6c501ad44d22"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24dfbafdee2946ef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16995,7 +16995,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98fbb4481e0e48ec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f11d6c3a62f467c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49906,7 +49906,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R557325160479418e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4efd4da5583b4c37"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -62421,10 +62421,10 @@
         <x:v>output/forms/对外确认表/01-门组做法确认表-发全屋定制.md</x:v>
       </x:c>
       <x:c r="I192" s="189" t="str">
-        <x:v>3a6fc947c3c6006ef4c06bc0cb3899268878d687e0fbf2e3ed8c6c7734b325ee</x:v>
+        <x:v>904376eb13c3aa6d70762f8665689a1c5358b702338c6ae60278e1793e934505</x:v>
       </x:c>
       <x:c r="J192" s="189" t="str">
-        <x:v>现行 Markdown；逐行已知信息／当前状态／只缺什么／责任方／回复附件</x:v>
+        <x:v>现行 Markdown；逐行说明已经知道什么／现在要做什么／由谁回答／在哪里回复</x:v>
       </x:c>
       <x:c r="K192" s="189" t="str">
         <x:v>D01-D13 已完成业主决定记录；不再作为外部填写入口</x:v>
@@ -62485,10 +62485,10 @@
         <x:v>output/forms/对外确认表/02-日立空调接口确认表-发空调厂家.md</x:v>
       </x:c>
       <x:c r="I193" s="189" t="str">
-        <x:v>de5e9c1ba8273a4a203bf53f42fddf4fd5df3cf5107ad85d9e47fa8443a5ef59</x:v>
+        <x:v>6e7b6b09ae5dbda788adfe48221cee8b6d0313b64e474d8c0cfcb7f357f8198d</x:v>
       </x:c>
       <x:c r="J193" s="189" t="str">
-        <x:v>现行 Markdown；逐行已知信息／当前状态／只缺什么／责任方／回复附件</x:v>
+        <x:v>现行 Markdown；逐行说明已经知道什么／现在要做什么／由谁回答／在哪里回复</x:v>
       </x:c>
       <x:c r="K193" s="189" t="str">
         <x:v>A01-A04 型号族、裸管径、官方保温边界及 PC-P1HEQ 通用接线已预填；只保留外部接口</x:v>
@@ -62549,16 +62549,16 @@
         <x:v>output/forms/对外确认表/03-给排水设备确认表-发设备与施工方.md</x:v>
       </x:c>
       <x:c r="I194" s="189" t="str">
-        <x:v>956f5df26790e746f84065e0e7c789f03e6b6b0c6388964e5abb50f1845a1c3f</x:v>
+        <x:v>04fdf90486f46bb8f2152f56034df4677e85616c2d9b9d6807b768b4e949e291</x:v>
       </x:c>
       <x:c r="J194" s="189" t="str">
-        <x:v>现行 Markdown；逐行已知信息／当前状态／只缺什么／责任方／回复附件</x:v>
+        <x:v>现行 Markdown；逐行说明已经知道什么／现在要做什么／由谁回答／在哪里回复</x:v>
       </x:c>
       <x:c r="K194" s="189" t="str">
         <x:v>洗烘、现行吉博力、定制地漏、石材盆及 APP-014 套管边界已预填</x:v>
       </x:c>
       <x:c r="L194" s="189" t="str">
-        <x:v>旧 MS 回复已拆为 confirmed owner decision、official/research conclusion、external pending 和 unknown</x:v>
+        <x:v>旧 MS 回复已拆成已由业主决定、已有官方资料、仍需外部回答和确实未知四类，不再把机器状态词显示给收件人</x:v>
       </x:c>
       <x:c r="M194" s="189" t="str">
         <x:v>准确双口墙排、项目节点、定制产品加工图或任何接口中心已冻结</x:v>
@@ -62613,10 +62613,10 @@
         <x:v>output/forms/对外确认表/04-燃气消防确认表-发主管单位.md</x:v>
       </x:c>
       <x:c r="I195" s="189" t="str">
-        <x:v>972d0ecb17828ca5315f3df46e5417e9e03d78a73e03e1fee9c8cb50158694d1</x:v>
+        <x:v>6d9bf349e756d4c69e94bd270f2eff765714fcff87296803051f7113ebfe8b5a</x:v>
       </x:c>
       <x:c r="J195" s="189" t="str">
-        <x:v>现行 Markdown；逐行已知信息／当前状态／只缺什么／责任方／回复附件</x:v>
+        <x:v>现行 Markdown；逐行说明已经知道什么／现在要做什么／由谁回答／在哪里回复</x:v>
       </x:c>
       <x:c r="K195" s="189" t="str">
         <x:v>ER9EPA33MP 燃气事实、报警联动决定和消防点位已预填；候选产品保持候选</x:v>
@@ -62677,10 +62677,10 @@
         <x:v>output/forms/对外确认表/05-弱电现场记录表-发现场负责人.md</x:v>
       </x:c>
       <x:c r="I196" s="189" t="str">
-        <x:v>71a70268dd01589be7ade57c5a3e23d73df5860f447f89df83aa74b7efb04959</x:v>
+        <x:v>597e82ddf445cd2782dfe43006a26c0cc9c34ea0d38789aa342b30dc02f520a4</x:v>
       </x:c>
       <x:c r="J196" s="189" t="str">
-        <x:v>现行 Markdown；逐行已知信息／当前状态／只缺什么／责任方／回复附件</x:v>
+        <x:v>现行 Markdown；逐行说明已经知道什么／现在要做什么／由谁回答／在哪里回复</x:v>
       </x:c>
       <x:c r="K196" s="189" t="str">
         <x:v>弱电箱约 110 mm、距墙 525 mm、H+350、CAD 坐标、柜格位置、五孔插座及五张照片已预填</x:v>
@@ -63409,10 +63409,10 @@
         <x:v>output/forms/对外确认表/06-门组厂家复核表-发Rimadesio与Poliform.md</x:v>
       </x:c>
       <x:c r="I207" s="189" t="str">
-        <x:v>ddd78b48be858ef8cfa18b48b0a801ce57c725c691f9e44cc3ac60b696611a12</x:v>
+        <x:v>f8835af1a36be93cf8d7d147e621c3536c9be8ced53074316be023580863cbd2</x:v>
       </x:c>
       <x:c r="J207" s="189" t="str">
-        <x:v>现行 Markdown；逐行已知信息／当前状态／只缺什么／责任方／回复附件</x:v>
+        <x:v>现行 Markdown；逐行说明已经知道什么／现在要做什么／由谁回答／在哪里回复</x:v>
       </x:c>
       <x:c r="K207" s="189" t="str">
         <x:v>业主既定门组方案转换为厂家是／否复核并要求回项目加工图</x:v>
@@ -63473,10 +63473,10 @@
         <x:v>output/forms/对外确认表/07-智能面板电气接口确认表-发JINK与电气方.md</x:v>
       </x:c>
       <x:c r="I208" s="189" t="str">
-        <x:v>78a0bd07b380940bd78a3d4c615781e2eaba3b5402a5c936cfc00f20df59c39d</x:v>
+        <x:v>ba23e3053767efa53edfa2414b75cf25951e7960b8ed7f2af879080fc6e04b1e</x:v>
       </x:c>
       <x:c r="J208" s="189" t="str">
-        <x:v>现行 Markdown；逐行已知信息／当前状态／只缺什么／责任方／回复附件</x:v>
+        <x:v>现行 Markdown；逐行说明已经知道什么／现在要做什么／由谁回答／在哪里回复</x:v>
       </x:c>
       <x:c r="K208" s="189" t="str">
         <x:v>Entry A、Master A、Master B 数量、键序、负载和双控关系已预填</x:v>
@@ -63537,10 +63537,10 @@
         <x:v>output/forms/对外确认表/08-定制家具与墙脚节点确认表-发全屋定制.md</x:v>
       </x:c>
       <x:c r="I209" s="189" t="str">
-        <x:v>602b2be4cba9030450b20eab53c649274c57d4b4d49aca334b8ceae741b10967</x:v>
+        <x:v>343c1e3d8bf720cd9640a132e7d838ec7ca1cd3139c4760e29bd2949a9473751</x:v>
       </x:c>
       <x:c r="J209" s="189" t="str">
-        <x:v>现行 Markdown；逐行已知信息／当前状态／只缺什么／责任方／回复附件</x:v>
+        <x:v>现行 Markdown；逐行说明已经知道什么／现在要做什么／由谁回答／在哪里回复</x:v>
       </x:c>
       <x:c r="K209" s="189" t="str">
         <x:v>服务塔候选尺寸和干区踢脚参考候选状态已预填</x:v>
@@ -63869,10 +63869,10 @@
         <x:v>output/forms/对外确认表/09-厨房设备与柜体深化确认表-发橱柜设备方.md</x:v>
       </x:c>
       <x:c r="I214" s="189" t="str">
-        <x:v>922f9b66f0f734632bebcc358e59b9f457a15ac8fbba4e02fe5fe50d87d35cf8</x:v>
+        <x:v>bfa07e88ddaac8fb44091963e9e5e5b5540cc5614d51ac0dbab67e67ea1bd600</x:v>
       </x:c>
       <x:c r="J214" s="189" t="str">
-        <x:v>现行 Markdown；逐行已知信息／当前状态／只缺什么／责任方／回复附件</x:v>
+        <x:v>现行 Markdown；逐行说明已经知道什么／现在要做什么／由谁回答／在哪里回复</x:v>
       </x:c>
       <x:c r="K214" s="189" t="str">
         <x:v>VVD 材料、Foster 参数、准确油烟机、厨房墙面、设备电气语义及候选边界已预填</x:v>
@@ -64179,7 +64179,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f804ed9bd614a3c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R761cf39fc6674081"/>
   </x:tableParts>
 </x:worksheet>
 </file>